--- a/research/traditional_assets/database/data/portugal/portugal_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_auto_truck.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1060292532576925</v>
+        <v>0.1058421418258513</v>
       </c>
       <c r="C2">
-        <v>294.070321502335</v>
+        <v>291.4420725349669</v>
       </c>
       <c r="D2">
-        <v>272.970321502335</v>
+        <v>273.3030725349669</v>
       </c>
       <c r="E2">
-        <v>-98.59999999999999</v>
+        <v>-95.639</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.961</v>
       </c>
       <c r="G2">
         <v>21.1</v>
@@ -1451,28 +1451,28 @@
         <v>31</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1489383</v>
       </c>
       <c r="N2">
-        <v>31</v>
+        <v>30.8510617</v>
       </c>
       <c r="O2">
-        <v>6.509999999999999</v>
+        <v>6.478722956999999</v>
       </c>
       <c r="P2">
-        <v>24.49</v>
+        <v>24.372338743</v>
       </c>
       <c r="Q2">
-        <v>52.79</v>
+        <v>52.672338743</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1060292532576925</v>
+        <v>0.106509870531163</v>
       </c>
       <c r="T2">
-        <v>1.015551736571413</v>
+        <v>1.023655634267286</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>208.1398807425625</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1058421418258513</v>
+        <v>0.1056550303940102</v>
       </c>
       <c r="C3">
-        <v>291.4420725349669</v>
+        <v>288.8146358052484</v>
       </c>
       <c r="D3">
-        <v>273.3030725349669</v>
+        <v>273.6366358052484</v>
       </c>
       <c r="E3">
-        <v>-95.639</v>
+        <v>-92.678</v>
       </c>
       <c r="F3">
-        <v>2.961</v>
+        <v>5.922000000000001</v>
       </c>
       <c r="G3">
         <v>21.1</v>
@@ -1533,28 +1533,28 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>0.1489383</v>
+        <v>0.2978766</v>
       </c>
       <c r="N3">
-        <v>30.8510617</v>
+        <v>30.7021234</v>
       </c>
       <c r="O3">
-        <v>6.478722956999999</v>
+        <v>6.447445913999999</v>
       </c>
       <c r="P3">
-        <v>24.372338743</v>
+        <v>24.254677486</v>
       </c>
       <c r="Q3">
-        <v>52.672338743</v>
+        <v>52.554677486</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.106509870531163</v>
+        <v>0.1070002963204186</v>
       </c>
       <c r="T3">
-        <v>1.023655634267286</v>
+        <v>1.031924917630422</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>208.1398807425625</v>
+        <v>104.0699403712813</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1056550303940102</v>
+        <v>0.105467918962169</v>
       </c>
       <c r="C4">
-        <v>288.8146358052484</v>
+        <v>286.1880142907939</v>
       </c>
       <c r="D4">
-        <v>273.6366358052484</v>
+        <v>273.9710142907939</v>
       </c>
       <c r="E4">
-        <v>-92.678</v>
+        <v>-89.717</v>
       </c>
       <c r="F4">
-        <v>5.922000000000001</v>
+        <v>8.883000000000001</v>
       </c>
       <c r="G4">
         <v>21.1</v>
@@ -1615,28 +1615,28 @@
         <v>31</v>
       </c>
       <c r="M4">
-        <v>0.2978766</v>
+        <v>0.4468149</v>
       </c>
       <c r="N4">
-        <v>30.7021234</v>
+        <v>30.5531851</v>
       </c>
       <c r="O4">
-        <v>6.447445913999999</v>
+        <v>6.416168870999999</v>
       </c>
       <c r="P4">
-        <v>24.254677486</v>
+        <v>24.137016229</v>
       </c>
       <c r="Q4">
-        <v>52.554677486</v>
+        <v>52.43701622899999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1070002963204186</v>
+        <v>0.1075008339816176</v>
       </c>
       <c r="T4">
-        <v>1.031924917630422</v>
+        <v>1.040364701681457</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>104.0699403712813</v>
+        <v>69.37996024752083</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.105467918962169</v>
+        <v>0.1052808075303279</v>
       </c>
       <c r="C5">
-        <v>286.1880142907939</v>
+        <v>283.56221098379</v>
       </c>
       <c r="D5">
-        <v>273.9710142907939</v>
+        <v>274.3062109837899</v>
       </c>
       <c r="E5">
-        <v>-89.717</v>
+        <v>-86.756</v>
       </c>
       <c r="F5">
-        <v>8.883000000000001</v>
+        <v>11.844</v>
       </c>
       <c r="G5">
         <v>21.1</v>
@@ -1697,28 +1697,28 @@
         <v>31</v>
       </c>
       <c r="M5">
-        <v>0.4468149</v>
+        <v>0.5957532</v>
       </c>
       <c r="N5">
-        <v>30.5531851</v>
+        <v>30.4042468</v>
       </c>
       <c r="O5">
-        <v>6.416168870999999</v>
+        <v>6.384891827999999</v>
       </c>
       <c r="P5">
-        <v>24.137016229</v>
+        <v>24.019354972</v>
       </c>
       <c r="Q5">
-        <v>52.43701622899999</v>
+        <v>52.319354972</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1075008339816176</v>
+        <v>0.1080117995107582</v>
       </c>
       <c r="T5">
-        <v>1.040364701681457</v>
+        <v>1.048980314566889</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.37996024752083</v>
+        <v>52.03497018564062</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1052808075303279</v>
+        <v>0.1050936960984867</v>
       </c>
       <c r="C6">
-        <v>283.56221098379</v>
+        <v>280.9372288910845</v>
       </c>
       <c r="D6">
-        <v>274.3062109837899</v>
+        <v>274.6422288910845</v>
       </c>
       <c r="E6">
-        <v>-86.756</v>
+        <v>-83.79499999999999</v>
       </c>
       <c r="F6">
-        <v>11.844</v>
+        <v>14.805</v>
       </c>
       <c r="G6">
         <v>21.1</v>
@@ -1779,28 +1779,28 @@
         <v>31</v>
       </c>
       <c r="M6">
-        <v>0.5957532</v>
+        <v>0.7446915000000001</v>
       </c>
       <c r="N6">
-        <v>30.4042468</v>
+        <v>30.2553085</v>
       </c>
       <c r="O6">
-        <v>6.384891827999999</v>
+        <v>6.353614785</v>
       </c>
       <c r="P6">
-        <v>24.019354972</v>
+        <v>23.901693715</v>
       </c>
       <c r="Q6">
-        <v>52.319354972</v>
+        <v>52.201693715</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1080117995107582</v>
+        <v>0.1085335222089334</v>
       </c>
       <c r="T6">
-        <v>1.048980314566889</v>
+        <v>1.057777308776225</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.03497018564062</v>
+        <v>41.6279761485125</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1050936960984867</v>
+        <v>0.1049065846666456</v>
       </c>
       <c r="C7">
-        <v>280.9372288910845</v>
+        <v>278.3130710342768</v>
       </c>
       <c r="D7">
-        <v>274.6422288910845</v>
+        <v>274.9790710342768</v>
       </c>
       <c r="E7">
-        <v>-83.79499999999999</v>
+        <v>-80.83399999999999</v>
       </c>
       <c r="F7">
-        <v>14.805</v>
+        <v>17.766</v>
       </c>
       <c r="G7">
         <v>21.1</v>
@@ -1861,28 +1861,28 @@
         <v>31</v>
       </c>
       <c r="M7">
-        <v>0.7446915000000001</v>
+        <v>0.8936298</v>
       </c>
       <c r="N7">
-        <v>30.2553085</v>
+        <v>30.1063702</v>
       </c>
       <c r="O7">
-        <v>6.353614785</v>
+        <v>6.322337741999999</v>
       </c>
       <c r="P7">
-        <v>23.901693715</v>
+        <v>23.784032458</v>
       </c>
       <c r="Q7">
-        <v>52.201693715</v>
+        <v>52.084032458</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1085335222089334</v>
+        <v>0.1090663453900485</v>
       </c>
       <c r="T7">
-        <v>1.057777308776225</v>
+        <v>1.06676147307512</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.6279761485125</v>
+        <v>34.68998012376041</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1049065846666456</v>
+        <v>0.1047194732348045</v>
       </c>
       <c r="C8">
-        <v>278.3130710342768</v>
+        <v>275.689740449808</v>
       </c>
       <c r="D8">
-        <v>274.9790710342768</v>
+        <v>275.3167404498079</v>
       </c>
       <c r="E8">
-        <v>-80.83399999999999</v>
+        <v>-77.87299999999999</v>
       </c>
       <c r="F8">
-        <v>17.766</v>
+        <v>20.727</v>
       </c>
       <c r="G8">
         <v>21.1</v>
@@ -1943,28 +1943,28 @@
         <v>31</v>
       </c>
       <c r="M8">
-        <v>0.8936298</v>
+        <v>1.0425681</v>
       </c>
       <c r="N8">
-        <v>30.1063702</v>
+        <v>29.9574319</v>
       </c>
       <c r="O8">
-        <v>6.322337741999999</v>
+        <v>6.291060698999999</v>
       </c>
       <c r="P8">
-        <v>23.784032458</v>
+        <v>23.666371201</v>
       </c>
       <c r="Q8">
-        <v>52.084032458</v>
+        <v>51.966371201</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1090663453900485</v>
+        <v>0.1096106271341983</v>
       </c>
       <c r="T8">
-        <v>1.06676147307512</v>
+        <v>1.075938845208402</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.68998012376041</v>
+        <v>29.73426867750893</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1047194732348044</v>
+        <v>0.1045323618029633</v>
       </c>
       <c r="C9">
-        <v>275.6897404498079</v>
+        <v>273.0672401890523</v>
       </c>
       <c r="D9">
-        <v>275.3167404498079</v>
+        <v>275.6552401890523</v>
       </c>
       <c r="E9">
-        <v>-77.87299999999999</v>
+        <v>-74.91199999999999</v>
       </c>
       <c r="F9">
-        <v>20.727</v>
+        <v>23.688</v>
       </c>
       <c r="G9">
         <v>21.1</v>
@@ -2025,28 +2025,28 @@
         <v>31</v>
       </c>
       <c r="M9">
-        <v>1.0425681</v>
+        <v>1.1915064</v>
       </c>
       <c r="N9">
-        <v>29.9574319</v>
+        <v>29.80849359999999</v>
       </c>
       <c r="O9">
-        <v>6.291060698999999</v>
+        <v>6.259783655999999</v>
       </c>
       <c r="P9">
-        <v>23.666371201</v>
+        <v>23.548709944</v>
       </c>
       <c r="Q9">
-        <v>51.966371201</v>
+        <v>51.84870994399999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1096106271341983</v>
+        <v>0.1101667410901775</v>
       </c>
       <c r="T9">
-        <v>1.075938845208402</v>
+        <v>1.085315725431536</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.73426867750892</v>
+        <v>26.01748509282031</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1045323618029633</v>
+        <v>0.1043452503711221</v>
       </c>
       <c r="C10">
-        <v>273.0672401890523</v>
+        <v>270.445573318409</v>
       </c>
       <c r="D10">
-        <v>275.6552401890523</v>
+        <v>275.994573318409</v>
       </c>
       <c r="E10">
-        <v>-74.91199999999999</v>
+        <v>-71.95099999999999</v>
       </c>
       <c r="F10">
-        <v>23.688</v>
+        <v>26.649</v>
       </c>
       <c r="G10">
         <v>21.1</v>
@@ -2107,28 +2107,28 @@
         <v>31</v>
       </c>
       <c r="M10">
-        <v>1.1915064</v>
+        <v>1.3404447</v>
       </c>
       <c r="N10">
-        <v>29.80849359999999</v>
+        <v>29.6595553</v>
       </c>
       <c r="O10">
-        <v>6.259783655999999</v>
+        <v>6.228506613</v>
       </c>
       <c r="P10">
-        <v>23.548709944</v>
+        <v>23.431048687</v>
       </c>
       <c r="Q10">
-        <v>51.84870994399999</v>
+        <v>51.731048687</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1101667410901775</v>
+        <v>0.1107350773309034</v>
       </c>
       <c r="T10">
-        <v>1.085315725431536</v>
+        <v>1.0948986909343</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.01748509282031</v>
+        <v>23.12665341584028</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1043452503711221</v>
+        <v>0.104158138939281</v>
       </c>
       <c r="C11">
-        <v>270.445573318409</v>
+        <v>267.824742919395</v>
       </c>
       <c r="D11">
-        <v>275.994573318409</v>
+        <v>276.334742919395</v>
       </c>
       <c r="E11">
-        <v>-71.95099999999999</v>
+        <v>-68.98999999999999</v>
       </c>
       <c r="F11">
-        <v>26.649</v>
+        <v>29.61</v>
       </c>
       <c r="G11">
         <v>21.1</v>
@@ -2189,28 +2189,28 @@
         <v>31</v>
       </c>
       <c r="M11">
-        <v>1.3404447</v>
+        <v>1.489383</v>
       </c>
       <c r="N11">
-        <v>29.6595553</v>
+        <v>29.510617</v>
       </c>
       <c r="O11">
-        <v>6.228506613</v>
+        <v>6.197229569999999</v>
       </c>
       <c r="P11">
-        <v>23.431048687</v>
+        <v>23.31338743</v>
       </c>
       <c r="Q11">
-        <v>51.731048687</v>
+        <v>51.61338743</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1107350773309034</v>
+        <v>0.1113160432658677</v>
       </c>
       <c r="T11">
-        <v>1.0948986909343</v>
+        <v>1.104694611226015</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.12665341584028</v>
+        <v>20.81398807425625</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.104158138939281</v>
+        <v>0.1039710275074398</v>
       </c>
       <c r="C12">
-        <v>267.824742919395</v>
+        <v>265.2047520887382</v>
       </c>
       <c r="D12">
-        <v>276.334742919395</v>
+        <v>276.6757520887382</v>
       </c>
       <c r="E12">
-        <v>-68.98999999999999</v>
+        <v>-66.029</v>
       </c>
       <c r="F12">
-        <v>29.61</v>
+        <v>32.57100000000001</v>
       </c>
       <c r="G12">
         <v>21.1</v>
@@ -2271,28 +2271,28 @@
         <v>31</v>
       </c>
       <c r="M12">
-        <v>1.489383</v>
+        <v>1.6383213</v>
       </c>
       <c r="N12">
-        <v>29.510617</v>
+        <v>29.3616787</v>
       </c>
       <c r="O12">
-        <v>6.197229569999999</v>
+        <v>6.165952526999999</v>
       </c>
       <c r="P12">
-        <v>23.31338743</v>
+        <v>23.195726173</v>
       </c>
       <c r="Q12">
-        <v>51.61338743</v>
+        <v>51.49572617299999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1113160432658677</v>
+        <v>0.1119100646151009</v>
       </c>
       <c r="T12">
-        <v>1.104694611226015</v>
+        <v>1.114710664557993</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.81398807425625</v>
+        <v>18.92180734023295</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1039710275074398</v>
+        <v>0.1037839160755987</v>
       </c>
       <c r="C13">
-        <v>265.2047520887382</v>
+        <v>262.5856039384713</v>
       </c>
       <c r="D13">
-        <v>276.6757520887382</v>
+        <v>277.0176039384713</v>
       </c>
       <c r="E13">
-        <v>-66.029</v>
+        <v>-63.06799999999999</v>
       </c>
       <c r="F13">
-        <v>32.57100000000001</v>
+        <v>35.532</v>
       </c>
       <c r="G13">
         <v>21.1</v>
@@ -2353,28 +2353,28 @@
         <v>31</v>
       </c>
       <c r="M13">
-        <v>1.6383213</v>
+        <v>1.7872596</v>
       </c>
       <c r="N13">
-        <v>29.3616787</v>
+        <v>29.2127404</v>
       </c>
       <c r="O13">
-        <v>6.165952526999999</v>
+        <v>6.134675484</v>
       </c>
       <c r="P13">
-        <v>23.195726173</v>
+        <v>23.078064916</v>
       </c>
       <c r="Q13">
-        <v>51.49572617299999</v>
+        <v>51.378064916</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1119100646151009</v>
+        <v>0.1125175864495439</v>
       </c>
       <c r="T13">
-        <v>1.114710664557993</v>
+        <v>1.124954355465697</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.92180734023295</v>
+        <v>17.34499006188021</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1037839160755987</v>
+        <v>0.1035968046437575</v>
       </c>
       <c r="C14">
-        <v>262.5856039384713</v>
+        <v>259.9673015960263</v>
       </c>
       <c r="D14">
-        <v>277.0176039384713</v>
+        <v>277.3603015960263</v>
       </c>
       <c r="E14">
-        <v>-63.06799999999999</v>
+        <v>-60.10699999999999</v>
       </c>
       <c r="F14">
-        <v>35.532</v>
+        <v>38.493</v>
       </c>
       <c r="G14">
         <v>21.1</v>
@@ -2435,28 +2435,28 @@
         <v>31</v>
       </c>
       <c r="M14">
-        <v>1.7872596</v>
+        <v>1.9361979</v>
       </c>
       <c r="N14">
-        <v>29.2127404</v>
+        <v>29.0638021</v>
       </c>
       <c r="O14">
-        <v>6.134675484</v>
+        <v>6.103398441</v>
       </c>
       <c r="P14">
-        <v>23.078064916</v>
+        <v>22.960403659</v>
       </c>
       <c r="Q14">
-        <v>51.378064916</v>
+        <v>51.260403659</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1125175864495439</v>
+        <v>0.1131390743031696</v>
       </c>
       <c r="T14">
-        <v>1.124954355465697</v>
+        <v>1.135433533520705</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.34499006188021</v>
+        <v>16.01076005712019</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1035968046437575</v>
+        <v>0.1034096932119164</v>
       </c>
       <c r="C15">
-        <v>259.9673015960263</v>
+        <v>257.3498482043307</v>
       </c>
       <c r="D15">
-        <v>277.3603015960263</v>
+        <v>277.7038482043307</v>
       </c>
       <c r="E15">
-        <v>-60.10699999999999</v>
+        <v>-57.14599999999999</v>
       </c>
       <c r="F15">
-        <v>38.493</v>
+        <v>41.45400000000001</v>
       </c>
       <c r="G15">
         <v>21.1</v>
@@ -2517,28 +2517,28 @@
         <v>31</v>
       </c>
       <c r="M15">
-        <v>1.9361979</v>
+        <v>2.0851362</v>
       </c>
       <c r="N15">
-        <v>29.0638021</v>
+        <v>28.9148638</v>
       </c>
       <c r="O15">
-        <v>6.103398441</v>
+        <v>6.072121397999999</v>
       </c>
       <c r="P15">
-        <v>22.960403659</v>
+        <v>22.842742402</v>
       </c>
       <c r="Q15">
-        <v>51.260403659</v>
+        <v>51.142742402</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1131390743031696</v>
+        <v>0.1137750153626934</v>
       </c>
       <c r="T15">
-        <v>1.135433533520705</v>
+        <v>1.146156413390946</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.01076005712019</v>
+        <v>14.86713433875446</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1034096932119164</v>
+        <v>0.1032225817800752</v>
       </c>
       <c r="C16">
-        <v>257.3498482043307</v>
+        <v>254.7332469219026</v>
       </c>
       <c r="D16">
-        <v>277.7038482043307</v>
+        <v>278.0482469219026</v>
       </c>
       <c r="E16">
-        <v>-57.14599999999999</v>
+        <v>-54.18499999999998</v>
       </c>
       <c r="F16">
-        <v>41.45400000000001</v>
+        <v>44.41500000000001</v>
       </c>
       <c r="G16">
         <v>21.1</v>
@@ -2599,28 +2599,28 @@
         <v>31</v>
       </c>
       <c r="M16">
-        <v>2.0851362</v>
+        <v>2.234074500000001</v>
       </c>
       <c r="N16">
-        <v>28.9148638</v>
+        <v>28.76592549999999</v>
       </c>
       <c r="O16">
-        <v>6.072121397999999</v>
+        <v>6.040844354999999</v>
       </c>
       <c r="P16">
-        <v>22.842742402</v>
+        <v>22.725081145</v>
       </c>
       <c r="Q16">
-        <v>51.142742402</v>
+        <v>51.025081145</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1137750153626934</v>
+        <v>0.1144259197412649</v>
       </c>
       <c r="T16">
-        <v>1.146156413390946</v>
+        <v>1.157131596316957</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.86713433875446</v>
+        <v>13.87599204950416</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1032225817800752</v>
+        <v>0.103035470348234</v>
       </c>
       <c r="C17">
-        <v>254.7332469219026</v>
+        <v>252.1175009229478</v>
       </c>
       <c r="D17">
-        <v>278.0482469219026</v>
+        <v>278.3935009229477</v>
       </c>
       <c r="E17">
-        <v>-54.185</v>
+        <v>-51.22399999999999</v>
       </c>
       <c r="F17">
-        <v>44.415</v>
+        <v>47.376</v>
       </c>
       <c r="G17">
         <v>21.1</v>
@@ -2681,28 +2681,28 @@
         <v>31</v>
       </c>
       <c r="M17">
-        <v>2.2340745</v>
+        <v>2.3830128</v>
       </c>
       <c r="N17">
-        <v>28.7659255</v>
+        <v>28.6169872</v>
       </c>
       <c r="O17">
-        <v>6.040844354999999</v>
+        <v>6.009567311999999</v>
       </c>
       <c r="P17">
-        <v>22.725081145</v>
+        <v>22.607419888</v>
       </c>
       <c r="Q17">
-        <v>51.025081145</v>
+        <v>50.907419888</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1144259197412649</v>
+        <v>0.1150923218431358</v>
       </c>
       <c r="T17">
-        <v>1.157131596316957</v>
+        <v>1.168368093122159</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.87599204950417</v>
+        <v>13.00874254641016</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.103035470348234</v>
+        <v>0.1030498089163929</v>
       </c>
       <c r="C18">
-        <v>252.1175009229478</v>
+        <v>249.1300133728096</v>
       </c>
       <c r="D18">
-        <v>278.3935009229477</v>
+        <v>278.3670133728096</v>
       </c>
       <c r="E18">
-        <v>-51.22399999999999</v>
+        <v>-48.26299999999998</v>
       </c>
       <c r="F18">
-        <v>47.376</v>
+        <v>50.33700000000001</v>
       </c>
       <c r="G18">
         <v>21.1</v>
@@ -2763,45 +2763,45 @@
         <v>31</v>
       </c>
       <c r="M18">
-        <v>2.3830128</v>
+        <v>2.6074566</v>
       </c>
       <c r="N18">
-        <v>28.6169872</v>
+        <v>28.3925434</v>
       </c>
       <c r="O18">
-        <v>6.009567311999999</v>
+        <v>5.962434114</v>
       </c>
       <c r="P18">
-        <v>22.607419888</v>
+        <v>22.430109286</v>
       </c>
       <c r="Q18">
-        <v>50.907419888</v>
+        <v>50.730109286</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1150923218431358</v>
+        <v>0.1157747818269794</v>
       </c>
       <c r="T18">
-        <v>1.168368093122159</v>
+        <v>1.179875348886523</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.21</v>
       </c>
       <c r="W18">
-        <v>0.039737</v>
+        <v>0.040922</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.00874254641016</v>
+        <v>11.88898024227901</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1030498089163929</v>
+        <v>0.1028745474845517</v>
       </c>
       <c r="C19">
-        <v>249.1300133728096</v>
+        <v>246.4931188711889</v>
       </c>
       <c r="D19">
-        <v>278.3670133728096</v>
+        <v>278.6911188711889</v>
       </c>
       <c r="E19">
-        <v>-48.26299999999998</v>
+        <v>-45.30199999999999</v>
       </c>
       <c r="F19">
-        <v>50.33700000000001</v>
+        <v>53.29800000000001</v>
       </c>
       <c r="G19">
         <v>21.1</v>
@@ -2845,28 +2845,28 @@
         <v>31</v>
       </c>
       <c r="M19">
-        <v>2.6074566</v>
+        <v>2.760836400000001</v>
       </c>
       <c r="N19">
-        <v>28.3925434</v>
+        <v>28.2391636</v>
       </c>
       <c r="O19">
-        <v>5.962434114</v>
+        <v>5.930224355999999</v>
       </c>
       <c r="P19">
-        <v>22.430109286</v>
+        <v>22.308939244</v>
       </c>
       <c r="Q19">
-        <v>50.730109286</v>
+        <v>50.608939244</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1157747818269794</v>
+        <v>0.1164738871762826</v>
       </c>
       <c r="T19">
-        <v>1.179875348886523</v>
+        <v>1.191663269425626</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.88898024227901</v>
+        <v>11.22848133993017</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1028745474845517</v>
+        <v>0.1026992860527106</v>
       </c>
       <c r="C20">
-        <v>246.4931188711889</v>
+        <v>243.8569799678669</v>
       </c>
       <c r="D20">
-        <v>278.6911188711889</v>
+        <v>279.0159799678669</v>
       </c>
       <c r="E20">
-        <v>-45.30199999999999</v>
+        <v>-42.34099999999999</v>
       </c>
       <c r="F20">
-        <v>53.298</v>
+        <v>56.25900000000001</v>
       </c>
       <c r="G20">
         <v>21.1</v>
@@ -2927,28 +2927,28 @@
         <v>31</v>
       </c>
       <c r="M20">
-        <v>2.7608364</v>
+        <v>2.9142162</v>
       </c>
       <c r="N20">
-        <v>28.2391636</v>
+        <v>28.08578379999999</v>
       </c>
       <c r="O20">
-        <v>5.930224355999999</v>
+        <v>5.898014597999999</v>
       </c>
       <c r="P20">
-        <v>22.308939244</v>
+        <v>22.18776920199999</v>
       </c>
       <c r="Q20">
-        <v>50.608939244</v>
+        <v>50.487769202</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1164738871762826</v>
+        <v>0.1171902543860625</v>
       </c>
       <c r="T20">
-        <v>1.191663269425626</v>
+        <v>1.203742249731128</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.22848133993017</v>
+        <v>10.63750863782858</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1026992860527106</v>
+        <v>0.1025240246208694</v>
       </c>
       <c r="C21">
-        <v>243.8569799678669</v>
+        <v>241.2215993082558</v>
       </c>
       <c r="D21">
-        <v>279.0159799678669</v>
+        <v>279.3415993082558</v>
       </c>
       <c r="E21">
-        <v>-42.34099999999999</v>
+        <v>-39.37999999999999</v>
       </c>
       <c r="F21">
-        <v>56.25900000000001</v>
+        <v>59.22000000000001</v>
       </c>
       <c r="G21">
         <v>21.1</v>
@@ -3009,28 +3009,28 @@
         <v>31</v>
       </c>
       <c r="M21">
-        <v>2.9142162</v>
+        <v>3.067596</v>
       </c>
       <c r="N21">
-        <v>28.08578379999999</v>
+        <v>27.93240399999999</v>
       </c>
       <c r="O21">
-        <v>5.898014597999999</v>
+        <v>5.865804839999998</v>
       </c>
       <c r="P21">
-        <v>22.18776920199999</v>
+        <v>22.06659916</v>
       </c>
       <c r="Q21">
-        <v>50.487769202</v>
+        <v>50.36659915999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1171902543860625</v>
+        <v>0.1179245307760868</v>
       </c>
       <c r="T21">
-        <v>1.203742249731128</v>
+        <v>1.216123204544267</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.63750863782858</v>
+        <v>10.10563320593715</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1025240246208694</v>
+        <v>0.1026307931890283</v>
       </c>
       <c r="C22">
-        <v>241.2215993082558</v>
+        <v>238.062142893116</v>
       </c>
       <c r="D22">
-        <v>279.3415993082558</v>
+        <v>279.143142893116</v>
       </c>
       <c r="E22">
-        <v>-39.37999999999999</v>
+        <v>-36.41899999999998</v>
       </c>
       <c r="F22">
-        <v>59.22000000000001</v>
+        <v>62.18100000000001</v>
       </c>
       <c r="G22">
         <v>21.1</v>
@@ -3091,45 +3091,45 @@
         <v>31</v>
       </c>
       <c r="M22">
-        <v>3.067596</v>
+        <v>3.326683500000001</v>
       </c>
       <c r="N22">
-        <v>27.93240399999999</v>
+        <v>27.67331649999999</v>
       </c>
       <c r="O22">
-        <v>5.865804839999998</v>
+        <v>5.811396464999999</v>
       </c>
       <c r="P22">
-        <v>22.06659916</v>
+        <v>21.861920035</v>
       </c>
       <c r="Q22">
-        <v>50.36659915999999</v>
+        <v>50.16192003499999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1179245307760868</v>
+        <v>0.1186773964418079</v>
       </c>
       <c r="T22">
-        <v>1.216123204544267</v>
+        <v>1.22881760125141</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.21</v>
       </c>
       <c r="W22">
-        <v>0.040922</v>
+        <v>0.042265</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.10563320593715</v>
+        <v>9.318590121362609</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1026307931890283</v>
+        <v>0.1024689617571871</v>
       </c>
       <c r="C23">
-        <v>238.062142893116</v>
+        <v>235.4020579119587</v>
       </c>
       <c r="D23">
-        <v>279.143142893116</v>
+        <v>279.4440579119586</v>
       </c>
       <c r="E23">
-        <v>-36.41899999999999</v>
+        <v>-33.45799999999998</v>
       </c>
       <c r="F23">
-        <v>62.181</v>
+        <v>65.14200000000001</v>
       </c>
       <c r="G23">
         <v>21.1</v>
@@ -3173,28 +3173,28 @@
         <v>31</v>
       </c>
       <c r="M23">
-        <v>3.3266835</v>
+        <v>3.485097000000001</v>
       </c>
       <c r="N23">
-        <v>27.67331649999999</v>
+        <v>27.514903</v>
       </c>
       <c r="O23">
-        <v>5.811396464999999</v>
+        <v>5.778129629999999</v>
       </c>
       <c r="P23">
-        <v>21.861920035</v>
+        <v>21.73677337</v>
       </c>
       <c r="Q23">
-        <v>50.16192003499999</v>
+        <v>50.03677337</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1186773964418079</v>
+        <v>0.1194495663553681</v>
       </c>
       <c r="T23">
-        <v>1.22881760125141</v>
+        <v>1.241837495310018</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.318590121362611</v>
+        <v>8.895017843118854</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1024689617571871</v>
+        <v>0.102307130325346</v>
       </c>
       <c r="C24">
-        <v>235.4020579119587</v>
+        <v>232.7426224009282</v>
       </c>
       <c r="D24">
-        <v>279.4440579119586</v>
+        <v>279.7456224009282</v>
       </c>
       <c r="E24">
-        <v>-33.45799999999998</v>
+        <v>-30.49699999999999</v>
       </c>
       <c r="F24">
-        <v>65.14200000000001</v>
+        <v>68.10300000000001</v>
       </c>
       <c r="G24">
         <v>21.1</v>
@@ -3255,28 +3255,28 @@
         <v>31</v>
       </c>
       <c r="M24">
-        <v>3.485097000000001</v>
+        <v>3.643510500000001</v>
       </c>
       <c r="N24">
-        <v>27.514903</v>
+        <v>27.3564895</v>
       </c>
       <c r="O24">
-        <v>5.778129629999999</v>
+        <v>5.744862794999999</v>
       </c>
       <c r="P24">
-        <v>21.73677337</v>
+        <v>21.611626705</v>
       </c>
       <c r="Q24">
-        <v>50.03677337</v>
+        <v>49.911626705</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1194495663553681</v>
+        <v>0.1202417926303194</v>
       </c>
       <c r="T24">
-        <v>1.241837495310018</v>
+        <v>1.255195568435083</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.895017843118854</v>
+        <v>8.508277936896295</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.102307130325346</v>
+        <v>0.1021452988935048</v>
       </c>
       <c r="C25">
-        <v>232.7426224009282</v>
+        <v>230.0838384649403</v>
       </c>
       <c r="D25">
-        <v>279.7456224009282</v>
+        <v>280.0478384649403</v>
       </c>
       <c r="E25">
-        <v>-30.49699999999999</v>
+        <v>-27.53599999999999</v>
       </c>
       <c r="F25">
-        <v>68.10300000000001</v>
+        <v>71.06400000000001</v>
       </c>
       <c r="G25">
         <v>21.1</v>
@@ -3337,28 +3337,28 @@
         <v>31</v>
       </c>
       <c r="M25">
-        <v>3.643510500000001</v>
+        <v>3.801924000000001</v>
       </c>
       <c r="N25">
-        <v>27.3564895</v>
+        <v>27.198076</v>
       </c>
       <c r="O25">
-        <v>5.744862794999999</v>
+        <v>5.711595959999999</v>
       </c>
       <c r="P25">
-        <v>21.611626705</v>
+        <v>21.48648004</v>
       </c>
       <c r="Q25">
-        <v>49.911626705</v>
+        <v>49.78648004</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1202417926303194</v>
+        <v>0.1210548669651379</v>
       </c>
       <c r="T25">
-        <v>1.255195568435083</v>
+        <v>1.268905169800281</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.508277936896295</v>
+        <v>8.153766356192284</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1021452988935048</v>
+        <v>0.1019834674616636</v>
       </c>
       <c r="C26">
-        <v>230.0838384649403</v>
+        <v>227.4257082180163</v>
       </c>
       <c r="D26">
-        <v>280.0478384649403</v>
+        <v>280.3507082180163</v>
       </c>
       <c r="E26">
-        <v>-27.53599999999999</v>
+        <v>-24.57499999999999</v>
       </c>
       <c r="F26">
-        <v>71.06400000000001</v>
+        <v>74.02500000000001</v>
       </c>
       <c r="G26">
         <v>21.1</v>
@@ -3419,28 +3419,28 @@
         <v>31</v>
       </c>
       <c r="M26">
-        <v>3.801924000000001</v>
+        <v>3.9603375</v>
       </c>
       <c r="N26">
-        <v>27.198076</v>
+        <v>27.0396625</v>
       </c>
       <c r="O26">
-        <v>5.711595959999999</v>
+        <v>5.678329124999999</v>
       </c>
       <c r="P26">
-        <v>21.48648004</v>
+        <v>21.361333375</v>
       </c>
       <c r="Q26">
-        <v>49.78648004</v>
+        <v>49.661333375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1210548669651379</v>
+        <v>0.1218896232822182</v>
       </c>
       <c r="T26">
-        <v>1.268905169800281</v>
+        <v>1.282980360535218</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.153766356192284</v>
+        <v>7.827615701944593</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1019834674616636</v>
+        <v>0.1019859560298225</v>
       </c>
       <c r="C27">
-        <v>227.4257082180163</v>
+        <v>224.4600458690442</v>
       </c>
       <c r="D27">
-        <v>280.3507082180163</v>
+        <v>280.3460458690442</v>
       </c>
       <c r="E27">
-        <v>-24.57499999999999</v>
+        <v>-21.61399999999999</v>
       </c>
       <c r="F27">
-        <v>74.02500000000001</v>
+        <v>76.986</v>
       </c>
       <c r="G27">
         <v>21.1</v>
@@ -3501,45 +3501,45 @@
         <v>31</v>
       </c>
       <c r="M27">
-        <v>3.9603375</v>
+        <v>4.1803398</v>
       </c>
       <c r="N27">
-        <v>27.0396625</v>
+        <v>26.81966019999999</v>
       </c>
       <c r="O27">
-        <v>5.678329124999999</v>
+        <v>5.632128641999999</v>
       </c>
       <c r="P27">
-        <v>21.361333375</v>
+        <v>21.187531558</v>
       </c>
       <c r="Q27">
-        <v>49.661333375</v>
+        <v>49.487531558</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1218896232822182</v>
+        <v>0.1227469405808412</v>
       </c>
       <c r="T27">
-        <v>1.282980360535218</v>
+        <v>1.297435961830559</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.21</v>
       </c>
       <c r="W27">
-        <v>0.042265</v>
+        <v>0.042897</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.827615701944593</v>
+        <v>7.415665109329148</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1019859560298225</v>
+        <v>0.1018304445979814</v>
       </c>
       <c r="C28">
-        <v>224.4600458690442</v>
+        <v>221.7906958183686</v>
       </c>
       <c r="D28">
-        <v>280.3460458690442</v>
+        <v>280.6376958183686</v>
       </c>
       <c r="E28">
-        <v>-21.61399999999999</v>
+        <v>-18.65299999999998</v>
       </c>
       <c r="F28">
-        <v>76.986</v>
+        <v>79.94700000000002</v>
       </c>
       <c r="G28">
         <v>21.1</v>
@@ -3583,28 +3583,28 @@
         <v>31</v>
       </c>
       <c r="M28">
-        <v>4.1803398</v>
+        <v>4.341122100000001</v>
       </c>
       <c r="N28">
-        <v>26.81966019999999</v>
+        <v>26.6588779</v>
       </c>
       <c r="O28">
-        <v>5.632128641999999</v>
+        <v>5.598364358999999</v>
       </c>
       <c r="P28">
-        <v>21.187531558</v>
+        <v>21.060513541</v>
       </c>
       <c r="Q28">
-        <v>49.487531558</v>
+        <v>49.360513541</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1227469405808412</v>
+        <v>0.123627746024632</v>
       </c>
       <c r="T28">
-        <v>1.297435961830559</v>
+        <v>1.312287606997006</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.415665109329148</v>
+        <v>7.141010846020662</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1018304445979814</v>
+        <v>0.1016749331661402</v>
       </c>
       <c r="C29">
-        <v>221.7906958183686</v>
+        <v>219.1219532189183</v>
       </c>
       <c r="D29">
-        <v>280.6376958183686</v>
+        <v>280.9299532189183</v>
       </c>
       <c r="E29">
-        <v>-18.65299999999998</v>
+        <v>-15.69199999999998</v>
       </c>
       <c r="F29">
-        <v>79.94700000000002</v>
+        <v>82.90800000000002</v>
       </c>
       <c r="G29">
         <v>21.1</v>
@@ -3665,28 +3665,28 @@
         <v>31</v>
       </c>
       <c r="M29">
-        <v>4.341122100000001</v>
+        <v>4.501904400000001</v>
       </c>
       <c r="N29">
-        <v>26.6588779</v>
+        <v>26.4980956</v>
       </c>
       <c r="O29">
-        <v>5.598364358999999</v>
+        <v>5.564600075999999</v>
       </c>
       <c r="P29">
-        <v>21.060513541</v>
+        <v>20.933495524</v>
       </c>
       <c r="Q29">
-        <v>49.360513541</v>
+        <v>49.233495524</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.123627746024632</v>
+        <v>0.1245330182863058</v>
       </c>
       <c r="T29">
-        <v>1.312287606997006</v>
+        <v>1.32755179786252</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.141010846020662</v>
+        <v>6.885974744377067</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1016749331661402</v>
+        <v>0.101519421734299</v>
       </c>
       <c r="C30">
-        <v>219.1219532189183</v>
+        <v>216.4538199704789</v>
       </c>
       <c r="D30">
-        <v>280.9299532189183</v>
+        <v>281.2228199704789</v>
       </c>
       <c r="E30">
-        <v>-15.69199999999998</v>
+        <v>-12.73099999999998</v>
       </c>
       <c r="F30">
-        <v>82.90800000000002</v>
+        <v>85.86900000000001</v>
       </c>
       <c r="G30">
         <v>21.1</v>
@@ -3747,28 +3747,28 @@
         <v>31</v>
       </c>
       <c r="M30">
-        <v>4.501904400000001</v>
+        <v>4.662686700000001</v>
       </c>
       <c r="N30">
-        <v>26.4980956</v>
+        <v>26.33731329999999</v>
       </c>
       <c r="O30">
-        <v>5.564600075999999</v>
+        <v>5.530835792999999</v>
       </c>
       <c r="P30">
-        <v>20.933495524</v>
+        <v>20.806477507</v>
       </c>
       <c r="Q30">
-        <v>49.233495524</v>
+        <v>49.10647750699999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1245330182863058</v>
+        <v>0.1254637911750691</v>
       </c>
       <c r="T30">
-        <v>1.32755179786252</v>
+        <v>1.343245965935513</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.885974744377067</v>
+        <v>6.648527339398546</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.101519421734299</v>
+        <v>0.1013639103024579</v>
       </c>
       <c r="C31">
-        <v>216.4538199704789</v>
+        <v>213.7862979807671</v>
       </c>
       <c r="D31">
-        <v>281.2228199704789</v>
+        <v>281.516297980767</v>
       </c>
       <c r="E31">
-        <v>-12.73099999999999</v>
+        <v>-9.769999999999996</v>
       </c>
       <c r="F31">
-        <v>85.869</v>
+        <v>88.83</v>
       </c>
       <c r="G31">
         <v>21.1</v>
@@ -3829,28 +3829,28 @@
         <v>31</v>
       </c>
       <c r="M31">
-        <v>4.6626867</v>
+        <v>4.823469</v>
       </c>
       <c r="N31">
-        <v>26.3373133</v>
+        <v>26.176531</v>
       </c>
       <c r="O31">
-        <v>5.530835793</v>
+        <v>5.49707151</v>
       </c>
       <c r="P31">
-        <v>20.806477507</v>
+        <v>20.67945949</v>
       </c>
       <c r="Q31">
-        <v>49.10647750699999</v>
+        <v>48.97945949</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1254637911750691</v>
+        <v>0.1264211575749398</v>
       </c>
       <c r="T31">
-        <v>1.343245965935513</v>
+        <v>1.359388538810592</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.648527339398548</v>
+        <v>6.426909761418597</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1013639103024579</v>
+        <v>0.1012083988706168</v>
       </c>
       <c r="C32">
-        <v>213.7862979807671</v>
+        <v>211.1193891654706</v>
       </c>
       <c r="D32">
-        <v>281.516297980767</v>
+        <v>281.8103891654706</v>
       </c>
       <c r="E32">
-        <v>-9.769999999999996</v>
+        <v>-6.808999999999983</v>
       </c>
       <c r="F32">
-        <v>88.83</v>
+        <v>91.79100000000001</v>
       </c>
       <c r="G32">
         <v>21.1</v>
@@ -3911,28 +3911,28 @@
         <v>31</v>
       </c>
       <c r="M32">
-        <v>4.823469</v>
+        <v>4.9842513</v>
       </c>
       <c r="N32">
-        <v>26.176531</v>
+        <v>26.0157487</v>
       </c>
       <c r="O32">
-        <v>5.49707151</v>
+        <v>5.463307226999999</v>
       </c>
       <c r="P32">
-        <v>20.67945949</v>
+        <v>20.552441473</v>
       </c>
       <c r="Q32">
-        <v>48.97945949</v>
+        <v>48.852441473</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1264211575749398</v>
+        <v>0.1274062737255315</v>
       </c>
       <c r="T32">
-        <v>1.359388538810592</v>
+        <v>1.375999012348716</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.426909761418597</v>
+        <v>6.219590091695416</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1012083988706168</v>
+        <v>0.1013056874387756</v>
       </c>
       <c r="C33">
-        <v>211.1193891654706</v>
+        <v>207.9743326416243</v>
       </c>
       <c r="D33">
-        <v>281.8103891654706</v>
+        <v>281.6263326416243</v>
       </c>
       <c r="E33">
-        <v>-6.808999999999983</v>
+        <v>-3.847999999999985</v>
       </c>
       <c r="F33">
-        <v>91.79100000000001</v>
+        <v>94.75200000000001</v>
       </c>
       <c r="G33">
         <v>21.1</v>
@@ -3993,45 +3993,45 @@
         <v>31</v>
       </c>
       <c r="M33">
-        <v>4.9842513</v>
+        <v>5.239785600000001</v>
       </c>
       <c r="N33">
-        <v>26.0157487</v>
+        <v>25.7602144</v>
       </c>
       <c r="O33">
-        <v>5.463307226999999</v>
+        <v>5.409645023999999</v>
       </c>
       <c r="P33">
-        <v>20.552441473</v>
+        <v>20.350569376</v>
       </c>
       <c r="Q33">
-        <v>48.852441473</v>
+        <v>48.65056937599999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1274062737255315</v>
+        <v>0.1284203638805523</v>
       </c>
       <c r="T33">
-        <v>1.375999012348716</v>
+        <v>1.393098029226197</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.21</v>
       </c>
       <c r="W33">
-        <v>0.042897</v>
+        <v>0.043687</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.219590091695416</v>
+        <v>5.916272604741688</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1013056874387756</v>
+        <v>0.1011580760069344</v>
       </c>
       <c r="C34">
-        <v>207.9743326416243</v>
+        <v>205.2926875040222</v>
       </c>
       <c r="D34">
-        <v>281.6263326416243</v>
+        <v>281.9056875040222</v>
       </c>
       <c r="E34">
-        <v>-3.847999999999985</v>
+        <v>-0.8869999999999862</v>
       </c>
       <c r="F34">
-        <v>94.75200000000001</v>
+        <v>97.71300000000001</v>
       </c>
       <c r="G34">
         <v>21.1</v>
@@ -4075,28 +4075,28 @@
         <v>31</v>
       </c>
       <c r="M34">
-        <v>5.239785600000001</v>
+        <v>5.4035289</v>
       </c>
       <c r="N34">
-        <v>25.7602144</v>
+        <v>25.5964711</v>
       </c>
       <c r="O34">
-        <v>5.409645023999999</v>
+        <v>5.375258930999999</v>
       </c>
       <c r="P34">
-        <v>20.350569376</v>
+        <v>20.221212169</v>
       </c>
       <c r="Q34">
-        <v>48.65056937599999</v>
+        <v>48.52121216899999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1284203638805523</v>
+        <v>0.1294647253834842</v>
       </c>
       <c r="T34">
-        <v>1.393098029226197</v>
+        <v>1.410707464517932</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.916272604741688</v>
+        <v>5.736991616719213</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1011580760069344</v>
+        <v>0.1010104645750933</v>
       </c>
       <c r="C35">
-        <v>205.2926875040222</v>
+        <v>202.6115971201249</v>
       </c>
       <c r="D35">
-        <v>281.9056875040222</v>
+        <v>282.185597120125</v>
       </c>
       <c r="E35">
-        <v>-0.8869999999999862</v>
+        <v>2.074000000000026</v>
       </c>
       <c r="F35">
-        <v>97.71300000000001</v>
+        <v>100.674</v>
       </c>
       <c r="G35">
         <v>21.1</v>
@@ -4157,28 +4157,28 @@
         <v>31</v>
       </c>
       <c r="M35">
-        <v>5.4035289</v>
+        <v>5.567272200000001</v>
       </c>
       <c r="N35">
-        <v>25.5964711</v>
+        <v>25.43272779999999</v>
       </c>
       <c r="O35">
-        <v>5.375258930999999</v>
+        <v>5.340872837999998</v>
       </c>
       <c r="P35">
-        <v>20.221212169</v>
+        <v>20.091854962</v>
       </c>
       <c r="Q35">
-        <v>48.52121216899999</v>
+        <v>48.391854962</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1294647253834842</v>
+        <v>0.1305407342046868</v>
       </c>
       <c r="T35">
-        <v>1.410707464517932</v>
+        <v>1.428850519060931</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.736991616719213</v>
+        <v>5.568256569168647</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1010104645750933</v>
+        <v>0.1008628531432521</v>
       </c>
       <c r="C36">
-        <v>202.6115971201249</v>
+        <v>199.9310631440522</v>
       </c>
       <c r="D36">
-        <v>282.185597120125</v>
+        <v>282.4660631440522</v>
       </c>
       <c r="E36">
-        <v>2.074000000000026</v>
+        <v>5.035000000000025</v>
       </c>
       <c r="F36">
-        <v>100.674</v>
+        <v>103.635</v>
       </c>
       <c r="G36">
         <v>21.1</v>
@@ -4239,28 +4239,28 @@
         <v>31</v>
       </c>
       <c r="M36">
-        <v>5.567272200000001</v>
+        <v>5.731015500000002</v>
       </c>
       <c r="N36">
-        <v>25.43272779999999</v>
+        <v>25.26898449999999</v>
       </c>
       <c r="O36">
-        <v>5.340872837999998</v>
+        <v>5.306486744999999</v>
       </c>
       <c r="P36">
-        <v>20.091854962</v>
+        <v>19.96249775499999</v>
       </c>
       <c r="Q36">
-        <v>48.391854962</v>
+        <v>48.262497755</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1305407342046868</v>
+        <v>0.1316498509896186</v>
       </c>
       <c r="T36">
-        <v>1.428850519060931</v>
+        <v>1.447551821436022</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.568256569168647</v>
+        <v>5.409163524335257</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1008628531432521</v>
+        <v>0.100715241711411</v>
       </c>
       <c r="C37">
-        <v>199.9310631440522</v>
+        <v>197.251087236506</v>
       </c>
       <c r="D37">
-        <v>282.4660631440522</v>
+        <v>282.747087236506</v>
       </c>
       <c r="E37">
-        <v>5.035000000000025</v>
+        <v>7.996000000000024</v>
       </c>
       <c r="F37">
-        <v>103.635</v>
+        <v>106.596</v>
       </c>
       <c r="G37">
         <v>21.1</v>
@@ -4321,28 +4321,28 @@
         <v>31</v>
       </c>
       <c r="M37">
-        <v>5.731015500000002</v>
+        <v>5.894758800000001</v>
       </c>
       <c r="N37">
-        <v>25.26898449999999</v>
+        <v>25.10524119999999</v>
       </c>
       <c r="O37">
-        <v>5.306486744999999</v>
+        <v>5.272100651999999</v>
       </c>
       <c r="P37">
-        <v>19.96249775499999</v>
+        <v>19.833140548</v>
       </c>
       <c r="Q37">
-        <v>48.262497755</v>
+        <v>48.133140548</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1316498509896186</v>
+        <v>0.1327936276740797</v>
       </c>
       <c r="T37">
-        <v>1.447551821436022</v>
+        <v>1.466837539510335</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.409163524335257</v>
+        <v>5.258908981992612</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.100715241711411</v>
+        <v>0.1005676302795698</v>
       </c>
       <c r="C38">
-        <v>197.251087236506</v>
+        <v>194.5716710648041</v>
       </c>
       <c r="D38">
-        <v>282.747087236506</v>
+        <v>283.0286710648041</v>
       </c>
       <c r="E38">
-        <v>7.996000000000009</v>
+        <v>10.95700000000001</v>
       </c>
       <c r="F38">
-        <v>106.596</v>
+        <v>109.557</v>
       </c>
       <c r="G38">
         <v>21.1</v>
@@ -4403,28 +4403,28 @@
         <v>31</v>
       </c>
       <c r="M38">
-        <v>5.8947588</v>
+        <v>6.0585021</v>
       </c>
       <c r="N38">
-        <v>25.10524119999999</v>
+        <v>24.94149789999999</v>
       </c>
       <c r="O38">
-        <v>5.272100651999999</v>
+        <v>5.237714558999999</v>
       </c>
       <c r="P38">
-        <v>19.833140548</v>
+        <v>19.703783341</v>
       </c>
       <c r="Q38">
-        <v>48.133140548</v>
+        <v>48.003783341</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1327936276740796</v>
+        <v>0.1339737147294759</v>
       </c>
       <c r="T38">
-        <v>1.466837539510335</v>
+        <v>1.48673550260288</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.258908981992612</v>
+        <v>5.116776306803623</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1005676302795698</v>
+        <v>0.1004200188477287</v>
       </c>
       <c r="C39">
-        <v>194.5716710648041</v>
+        <v>191.8928163029126</v>
       </c>
       <c r="D39">
-        <v>283.0286710648041</v>
+        <v>283.3108163029127</v>
       </c>
       <c r="E39">
-        <v>10.95700000000001</v>
+        <v>13.91800000000002</v>
       </c>
       <c r="F39">
-        <v>109.557</v>
+        <v>112.518</v>
       </c>
       <c r="G39">
         <v>21.1</v>
@@ -4485,28 +4485,28 @@
         <v>31</v>
       </c>
       <c r="M39">
-        <v>6.0585021</v>
+        <v>6.222245400000001</v>
       </c>
       <c r="N39">
-        <v>24.94149789999999</v>
+        <v>24.77775459999999</v>
       </c>
       <c r="O39">
-        <v>5.237714558999999</v>
+        <v>5.203328465999999</v>
       </c>
       <c r="P39">
-        <v>19.703783341</v>
+        <v>19.574426134</v>
       </c>
       <c r="Q39">
-        <v>48.003783341</v>
+        <v>47.874426134</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1339737147294759</v>
+        <v>0.1351918691092398</v>
       </c>
       <c r="T39">
-        <v>1.48673550260288</v>
+        <v>1.507275335472604</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.116776306803623</v>
+        <v>4.982124298729843</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1004200188477287</v>
+        <v>0.1002724074158875</v>
       </c>
       <c r="C40">
-        <v>191.8928163029126</v>
+        <v>189.2145246314794</v>
       </c>
       <c r="D40">
-        <v>283.3108163029127</v>
+        <v>283.5935246314794</v>
       </c>
       <c r="E40">
-        <v>13.91800000000002</v>
+        <v>16.87900000000002</v>
       </c>
       <c r="F40">
-        <v>112.518</v>
+        <v>115.479</v>
       </c>
       <c r="G40">
         <v>21.1</v>
@@ -4567,28 +4567,28 @@
         <v>31</v>
       </c>
       <c r="M40">
-        <v>6.222245400000001</v>
+        <v>6.385988700000001</v>
       </c>
       <c r="N40">
-        <v>24.77775459999999</v>
+        <v>24.61401129999999</v>
       </c>
       <c r="O40">
-        <v>5.203328465999999</v>
+        <v>5.168942372999998</v>
       </c>
       <c r="P40">
-        <v>19.574426134</v>
+        <v>19.44506892699999</v>
       </c>
       <c r="Q40">
-        <v>47.874426134</v>
+        <v>47.74506892699999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1351918691092398</v>
+        <v>0.1364499629768647</v>
       </c>
       <c r="T40">
-        <v>1.507275335472604</v>
+        <v>1.528488605485597</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.982124298729843</v>
+        <v>4.854377521839334</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1002724074158875</v>
+        <v>0.1001247959840463</v>
       </c>
       <c r="C41">
-        <v>189.2145246314794</v>
+        <v>186.5367977378671</v>
       </c>
       <c r="D41">
-        <v>283.5935246314794</v>
+        <v>283.876797737867</v>
       </c>
       <c r="E41">
-        <v>16.87900000000002</v>
+        <v>19.84000000000002</v>
       </c>
       <c r="F41">
-        <v>115.479</v>
+        <v>118.44</v>
       </c>
       <c r="G41">
         <v>21.1</v>
@@ -4649,28 +4649,28 @@
         <v>31</v>
       </c>
       <c r="M41">
-        <v>6.385988700000001</v>
+        <v>6.549732000000001</v>
       </c>
       <c r="N41">
-        <v>24.61401129999999</v>
+        <v>24.45026799999999</v>
       </c>
       <c r="O41">
-        <v>5.168942372999998</v>
+        <v>5.134556279999998</v>
       </c>
       <c r="P41">
-        <v>19.44506892699999</v>
+        <v>19.31571172</v>
       </c>
       <c r="Q41">
-        <v>47.74506892699999</v>
+        <v>47.61571171999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1364499629768647</v>
+        <v>0.1377499933067439</v>
       </c>
       <c r="T41">
-        <v>1.528488605485597</v>
+        <v>1.550408984499024</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.854377521839334</v>
+        <v>4.73301808379335</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1001247959840463</v>
+        <v>0.09997718455220519</v>
       </c>
       <c r="C42">
-        <v>186.5367977378671</v>
+        <v>183.8596373161869</v>
       </c>
       <c r="D42">
-        <v>283.876797737867</v>
+        <v>284.1606373161869</v>
       </c>
       <c r="E42">
-        <v>19.84000000000002</v>
+        <v>22.80100000000003</v>
       </c>
       <c r="F42">
-        <v>118.44</v>
+        <v>121.401</v>
       </c>
       <c r="G42">
         <v>21.1</v>
@@ -4731,28 +4731,28 @@
         <v>31</v>
       </c>
       <c r="M42">
-        <v>6.549732000000001</v>
+        <v>6.713475300000002</v>
       </c>
       <c r="N42">
-        <v>24.45026799999999</v>
+        <v>24.28652469999999</v>
       </c>
       <c r="O42">
-        <v>5.134556279999998</v>
+        <v>5.100170186999999</v>
       </c>
       <c r="P42">
-        <v>19.31571172</v>
+        <v>19.18635451299999</v>
       </c>
       <c r="Q42">
-        <v>47.61571171999999</v>
+        <v>47.48635451299999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1377499933067439</v>
+        <v>0.1390940924613647</v>
       </c>
       <c r="T42">
-        <v>1.550408984499024</v>
+        <v>1.573072427207821</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.73301808379335</v>
+        <v>4.617578618334976</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09997718455220519</v>
+        <v>0.09982957312036403</v>
       </c>
       <c r="C43">
-        <v>183.8596373161869</v>
+        <v>181.1830450673327</v>
       </c>
       <c r="D43">
-        <v>284.1606373161869</v>
+        <v>284.4450450673327</v>
       </c>
       <c r="E43">
-        <v>22.80100000000003</v>
+        <v>25.76200000000003</v>
       </c>
       <c r="F43">
-        <v>121.401</v>
+        <v>124.362</v>
       </c>
       <c r="G43">
         <v>21.1</v>
@@ -4813,28 +4813,28 @@
         <v>31</v>
       </c>
       <c r="M43">
-        <v>6.713475300000002</v>
+        <v>6.877218600000002</v>
       </c>
       <c r="N43">
-        <v>24.28652469999999</v>
+        <v>24.12278139999999</v>
       </c>
       <c r="O43">
-        <v>5.100170186999999</v>
+        <v>5.065784093999999</v>
       </c>
       <c r="P43">
-        <v>19.18635451299999</v>
+        <v>19.056997306</v>
       </c>
       <c r="Q43">
-        <v>47.48635451299999</v>
+        <v>47.356997306</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1390940924613647</v>
+        <v>0.1404845398626966</v>
       </c>
       <c r="T43">
-        <v>1.573072427207821</v>
+        <v>1.59651736794106</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.617578618334976</v>
+        <v>4.507636270279381</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09982957312036403</v>
+        <v>0.1005312116885229</v>
       </c>
       <c r="C44">
-        <v>181.1830450673327</v>
+        <v>176.8752295106174</v>
       </c>
       <c r="D44">
-        <v>284.4450450673327</v>
+        <v>283.0982295106174</v>
       </c>
       <c r="E44">
-        <v>25.76200000000001</v>
+        <v>28.72300000000001</v>
       </c>
       <c r="F44">
-        <v>124.362</v>
+        <v>127.323</v>
       </c>
       <c r="G44">
         <v>21.1</v>
@@ -4895,45 +4895,45 @@
         <v>31</v>
       </c>
       <c r="M44">
-        <v>6.877218600000001</v>
+        <v>7.359269400000001</v>
       </c>
       <c r="N44">
-        <v>24.12278139999999</v>
+        <v>23.64073059999999</v>
       </c>
       <c r="O44">
-        <v>5.065784093999999</v>
+        <v>4.964553425999998</v>
       </c>
       <c r="P44">
-        <v>19.056997306</v>
+        <v>18.676177174</v>
       </c>
       <c r="Q44">
-        <v>47.356997306</v>
+        <v>46.976177174</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1404845398626966</v>
+        <v>0.1419237748921454</v>
       </c>
       <c r="T44">
-        <v>1.596517367941059</v>
+        <v>1.620784938173709</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.21</v>
       </c>
       <c r="W44">
-        <v>0.043687</v>
+        <v>0.04566200000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.507636270279382</v>
+        <v>4.21237466860501</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1005312116885229</v>
+        <v>0.1004033502566817</v>
       </c>
       <c r="C45">
-        <v>176.8752295106174</v>
+        <v>174.1587120837025</v>
       </c>
       <c r="D45">
-        <v>283.0982295106174</v>
+        <v>283.3427120837025</v>
       </c>
       <c r="E45">
-        <v>28.72300000000001</v>
+        <v>31.68400000000003</v>
       </c>
       <c r="F45">
-        <v>127.323</v>
+        <v>130.284</v>
       </c>
       <c r="G45">
         <v>21.1</v>
@@ -4977,28 +4977,28 @@
         <v>31</v>
       </c>
       <c r="M45">
-        <v>7.359269400000001</v>
+        <v>7.530415200000002</v>
       </c>
       <c r="N45">
-        <v>23.64073059999999</v>
+        <v>23.46958479999999</v>
       </c>
       <c r="O45">
-        <v>4.964553425999998</v>
+        <v>4.928612807999999</v>
       </c>
       <c r="P45">
-        <v>18.676177174</v>
+        <v>18.540971992</v>
       </c>
       <c r="Q45">
-        <v>46.976177174</v>
+        <v>46.84097199199999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1419237748921454</v>
+        <v>0.1434144111726459</v>
       </c>
       <c r="T45">
-        <v>1.620784938173709</v>
+        <v>1.64591920734324</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.21237466860501</v>
+        <v>4.116638880682168</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1004033502566817</v>
+        <v>0.1002754888248406</v>
       </c>
       <c r="C46">
-        <v>174.1587120837025</v>
+        <v>171.4426172902453</v>
       </c>
       <c r="D46">
-        <v>283.3427120837025</v>
+        <v>283.5876172902452</v>
       </c>
       <c r="E46">
-        <v>31.68400000000003</v>
+        <v>34.64500000000001</v>
       </c>
       <c r="F46">
-        <v>130.284</v>
+        <v>133.245</v>
       </c>
       <c r="G46">
         <v>21.1</v>
@@ -5059,28 +5059,28 @@
         <v>31</v>
       </c>
       <c r="M46">
-        <v>7.530415200000002</v>
+        <v>7.701561000000001</v>
       </c>
       <c r="N46">
-        <v>23.46958479999999</v>
+        <v>23.29843899999999</v>
       </c>
       <c r="O46">
-        <v>4.928612807999999</v>
+        <v>4.892672189999999</v>
       </c>
       <c r="P46">
-        <v>18.540971992</v>
+        <v>18.40576681</v>
       </c>
       <c r="Q46">
-        <v>46.84097199199999</v>
+        <v>46.70576681</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1434144111726459</v>
+        <v>0.1449592524088011</v>
       </c>
       <c r="T46">
-        <v>1.64591920734324</v>
+        <v>1.671967449937118</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.116638880682168</v>
+        <v>4.02515801666701</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1002754888248406</v>
+        <v>0.1014195273929994</v>
       </c>
       <c r="C47">
-        <v>171.4426172902453</v>
+        <v>166.3052682053985</v>
       </c>
       <c r="D47">
-        <v>283.5876172902452</v>
+        <v>281.4112682053985</v>
       </c>
       <c r="E47">
-        <v>34.64500000000001</v>
+        <v>37.60600000000002</v>
       </c>
       <c r="F47">
-        <v>133.245</v>
+        <v>136.206</v>
       </c>
       <c r="G47">
         <v>21.1</v>
@@ -5141,45 +5141,45 @@
         <v>31</v>
       </c>
       <c r="M47">
-        <v>7.701561000000001</v>
+        <v>8.349427800000001</v>
       </c>
       <c r="N47">
-        <v>23.29843899999999</v>
+        <v>22.6505722</v>
       </c>
       <c r="O47">
-        <v>4.892672189999999</v>
+        <v>4.756620161999999</v>
       </c>
       <c r="P47">
-        <v>18.40576681</v>
+        <v>17.89395203799999</v>
       </c>
       <c r="Q47">
-        <v>46.70576681</v>
+        <v>46.19395203799999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1449592524088011</v>
+        <v>0.146561309987036</v>
       </c>
       <c r="T47">
-        <v>1.671967449937118</v>
+        <v>1.698980442256694</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.21</v>
       </c>
       <c r="W47">
-        <v>0.04566200000000001</v>
+        <v>0.048427</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.02515801666701</v>
+        <v>3.71282927915132</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1014195273929994</v>
+        <v>0.1013193159611583</v>
       </c>
       <c r="C48">
-        <v>166.3052682053985</v>
+        <v>163.5335685578154</v>
       </c>
       <c r="D48">
-        <v>281.4112682053985</v>
+        <v>281.6005685578154</v>
       </c>
       <c r="E48">
-        <v>37.60600000000002</v>
+        <v>40.56700000000004</v>
       </c>
       <c r="F48">
-        <v>136.206</v>
+        <v>139.167</v>
       </c>
       <c r="G48">
         <v>21.1</v>
@@ -5223,28 +5223,28 @@
         <v>31</v>
       </c>
       <c r="M48">
-        <v>8.349427800000001</v>
+        <v>8.530937100000003</v>
       </c>
       <c r="N48">
-        <v>22.6505722</v>
+        <v>22.46906289999999</v>
       </c>
       <c r="O48">
-        <v>4.756620161999999</v>
+        <v>4.718503208999999</v>
       </c>
       <c r="P48">
-        <v>17.89395203799999</v>
+        <v>17.750559691</v>
       </c>
       <c r="Q48">
-        <v>46.19395203799999</v>
+        <v>46.050559691</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.146561309987036</v>
+        <v>0.1482238225682231</v>
       </c>
       <c r="T48">
-        <v>1.698980442256694</v>
+        <v>1.727012792777009</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.71282927915132</v>
+        <v>3.633832911509802</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1013193159611583</v>
+        <v>0.1012191045293171</v>
       </c>
       <c r="C49">
-        <v>163.5335685578154</v>
+        <v>160.7621237596219</v>
       </c>
       <c r="D49">
-        <v>281.6005685578154</v>
+        <v>281.7901237596219</v>
       </c>
       <c r="E49">
-        <v>40.56700000000004</v>
+        <v>43.52800000000002</v>
       </c>
       <c r="F49">
-        <v>139.167</v>
+        <v>142.128</v>
       </c>
       <c r="G49">
         <v>21.1</v>
@@ -5305,28 +5305,28 @@
         <v>31</v>
       </c>
       <c r="M49">
-        <v>8.530937100000003</v>
+        <v>8.712446400000001</v>
       </c>
       <c r="N49">
-        <v>22.46906289999999</v>
+        <v>22.2875536</v>
       </c>
       <c r="O49">
-        <v>4.718503208999999</v>
+        <v>4.680386255999998</v>
       </c>
       <c r="P49">
-        <v>17.750559691</v>
+        <v>17.607167344</v>
       </c>
       <c r="Q49">
-        <v>46.050559691</v>
+        <v>45.907167344</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1482238225682231</v>
+        <v>0.1499502779409944</v>
       </c>
       <c r="T49">
-        <v>1.727012792777009</v>
+        <v>1.756123310625028</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.633832911509802</v>
+        <v>3.558128059186682</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1012191045293171</v>
+        <v>0.102202773097476</v>
       </c>
       <c r="C50">
-        <v>160.7621237596219</v>
+        <v>155.9514321137865</v>
       </c>
       <c r="D50">
-        <v>281.7901237596219</v>
+        <v>279.9404321137865</v>
       </c>
       <c r="E50">
-        <v>43.52800000000002</v>
+        <v>46.489</v>
       </c>
       <c r="F50">
-        <v>142.128</v>
+        <v>145.089</v>
       </c>
       <c r="G50">
         <v>21.1</v>
@@ -5387,45 +5387,45 @@
         <v>31</v>
       </c>
       <c r="M50">
-        <v>8.712446400000001</v>
+        <v>9.300204900000001</v>
       </c>
       <c r="N50">
-        <v>22.2875536</v>
+        <v>21.6997951</v>
       </c>
       <c r="O50">
-        <v>4.680386255999998</v>
+        <v>4.556956970999999</v>
       </c>
       <c r="P50">
-        <v>17.607167344</v>
+        <v>17.142838129</v>
       </c>
       <c r="Q50">
-        <v>45.907167344</v>
+        <v>45.44283812899999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1499502779409944</v>
+        <v>0.1517444374460313</v>
       </c>
       <c r="T50">
-        <v>1.756123310625028</v>
+        <v>1.786375417408264</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.21</v>
       </c>
       <c r="W50">
-        <v>0.048427</v>
+        <v>0.050639</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.558128059186682</v>
+        <v>3.33325989409115</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.102202773097476</v>
+        <v>0.1021246816656348</v>
       </c>
       <c r="C51">
-        <v>155.9514321137865</v>
+        <v>153.1363875116206</v>
       </c>
       <c r="D51">
-        <v>279.9404321137865</v>
+        <v>280.0863875116206</v>
       </c>
       <c r="E51">
-        <v>46.489</v>
+        <v>49.45000000000002</v>
       </c>
       <c r="F51">
-        <v>145.089</v>
+        <v>148.05</v>
       </c>
       <c r="G51">
         <v>21.1</v>
@@ -5469,28 +5469,28 @@
         <v>31</v>
       </c>
       <c r="M51">
-        <v>9.300204900000001</v>
+        <v>9.490005000000002</v>
       </c>
       <c r="N51">
-        <v>21.6997951</v>
+        <v>21.509995</v>
       </c>
       <c r="O51">
-        <v>4.556956970999999</v>
+        <v>4.517098949999999</v>
       </c>
       <c r="P51">
-        <v>17.142838129</v>
+        <v>16.99289605</v>
       </c>
       <c r="Q51">
-        <v>45.44283812899999</v>
+        <v>45.29289605</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1517444374460313</v>
+        <v>0.1536103633312696</v>
       </c>
       <c r="T51">
-        <v>1.786375417408264</v>
+        <v>1.817837608462829</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.33325989409115</v>
+        <v>3.266594696209327</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1021246816656348</v>
+        <v>0.1020465902337937</v>
       </c>
       <c r="C52">
-        <v>153.1363875116206</v>
+        <v>150.3214951853568</v>
       </c>
       <c r="D52">
-        <v>280.0863875116206</v>
+        <v>280.2324951853568</v>
       </c>
       <c r="E52">
-        <v>49.45000000000002</v>
+        <v>52.41100000000003</v>
       </c>
       <c r="F52">
-        <v>148.05</v>
+        <v>151.011</v>
       </c>
       <c r="G52">
         <v>21.1</v>
@@ -5551,28 +5551,28 @@
         <v>31</v>
       </c>
       <c r="M52">
-        <v>9.490005000000002</v>
+        <v>9.679805100000003</v>
       </c>
       <c r="N52">
-        <v>21.509995</v>
+        <v>21.32019489999999</v>
       </c>
       <c r="O52">
-        <v>4.517098949999999</v>
+        <v>4.477240928999999</v>
       </c>
       <c r="P52">
-        <v>16.99289605</v>
+        <v>16.84295397099999</v>
       </c>
       <c r="Q52">
-        <v>45.29289605</v>
+        <v>45.142953971</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1536103633312696</v>
+        <v>0.1555524494567218</v>
       </c>
       <c r="T52">
-        <v>1.817837608462829</v>
+        <v>1.850583970580847</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.266594696209327</v>
+        <v>3.202543819813065</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1020465902337937</v>
+        <v>0.1019684988019525</v>
       </c>
       <c r="C53">
-        <v>150.3214951853568</v>
+        <v>147.5067553734245</v>
       </c>
       <c r="D53">
-        <v>280.2324951853568</v>
+        <v>280.3787553734244</v>
       </c>
       <c r="E53">
-        <v>52.41100000000003</v>
+        <v>55.37200000000001</v>
       </c>
       <c r="F53">
-        <v>151.011</v>
+        <v>153.972</v>
       </c>
       <c r="G53">
         <v>21.1</v>
@@ -5633,28 +5633,28 @@
         <v>31</v>
       </c>
       <c r="M53">
-        <v>9.679805100000003</v>
+        <v>9.869605200000001</v>
       </c>
       <c r="N53">
-        <v>21.32019489999999</v>
+        <v>21.1303948</v>
       </c>
       <c r="O53">
-        <v>4.477240928999999</v>
+        <v>4.437382907999999</v>
       </c>
       <c r="P53">
-        <v>16.84295397099999</v>
+        <v>16.693011892</v>
       </c>
       <c r="Q53">
-        <v>45.142953971</v>
+        <v>44.993011892</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1555524494567218</v>
+        <v>0.157575455837401</v>
       </c>
       <c r="T53">
-        <v>1.850583970580847</v>
+        <v>1.884694764453781</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.202543819813065</v>
+        <v>3.140956438662815</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1019684988019525</v>
+        <v>0.1018904073701113</v>
       </c>
       <c r="C54">
-        <v>147.5067553734245</v>
+        <v>144.6921683147513</v>
       </c>
       <c r="D54">
-        <v>280.3787553734244</v>
+        <v>280.5251683147513</v>
       </c>
       <c r="E54">
-        <v>55.37200000000001</v>
+        <v>58.33300000000003</v>
       </c>
       <c r="F54">
-        <v>153.972</v>
+        <v>156.933</v>
       </c>
       <c r="G54">
         <v>21.1</v>
@@ -5715,28 +5715,28 @@
         <v>31</v>
       </c>
       <c r="M54">
-        <v>9.869605200000001</v>
+        <v>10.0594053</v>
       </c>
       <c r="N54">
-        <v>21.1303948</v>
+        <v>20.94059469999999</v>
       </c>
       <c r="O54">
-        <v>4.437382907999999</v>
+        <v>4.397524886999999</v>
       </c>
       <c r="P54">
-        <v>16.693011892</v>
+        <v>16.543069813</v>
       </c>
       <c r="Q54">
-        <v>44.993011892</v>
+        <v>44.843069813</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.157575455837401</v>
+        <v>0.1596845475959816</v>
       </c>
       <c r="T54">
-        <v>1.884694764453781</v>
+        <v>1.920257081470244</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.140956438662815</v>
+        <v>3.08169310963144</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1018904073701113</v>
+        <v>0.1018123159382702</v>
       </c>
       <c r="C55">
-        <v>144.6921683147513</v>
+        <v>141.877734248764</v>
       </c>
       <c r="D55">
-        <v>280.5251683147513</v>
+        <v>280.671734248764</v>
       </c>
       <c r="E55">
-        <v>58.33300000000003</v>
+        <v>61.29400000000004</v>
       </c>
       <c r="F55">
-        <v>156.933</v>
+        <v>159.894</v>
       </c>
       <c r="G55">
         <v>21.1</v>
@@ -5797,28 +5797,28 @@
         <v>31</v>
       </c>
       <c r="M55">
-        <v>10.0594053</v>
+        <v>10.2492054</v>
       </c>
       <c r="N55">
-        <v>20.94059469999999</v>
+        <v>20.75079459999999</v>
       </c>
       <c r="O55">
-        <v>4.397524886999999</v>
+        <v>4.357666865999998</v>
       </c>
       <c r="P55">
-        <v>16.543069813</v>
+        <v>16.39312773399999</v>
       </c>
       <c r="Q55">
-        <v>44.843069813</v>
+        <v>44.69312773399999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1596845475959816</v>
+        <v>0.1618853389962395</v>
       </c>
       <c r="T55">
-        <v>1.920257081470244</v>
+        <v>1.957365586183076</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.08169310963144</v>
+        <v>3.024624718712339</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1018123159382702</v>
+        <v>0.105123324506429</v>
       </c>
       <c r="C56">
-        <v>141.877734248764</v>
+        <v>132.8339668435306</v>
       </c>
       <c r="D56">
-        <v>280.671734248764</v>
+        <v>274.5889668435306</v>
       </c>
       <c r="E56">
-        <v>61.29400000000004</v>
+        <v>64.25500000000002</v>
       </c>
       <c r="F56">
-        <v>159.894</v>
+        <v>162.855</v>
       </c>
       <c r="G56">
         <v>21.1</v>
@@ -5879,45 +5879,45 @@
         <v>31</v>
       </c>
       <c r="M56">
-        <v>10.2492054</v>
+        <v>11.7092745</v>
       </c>
       <c r="N56">
-        <v>20.75079459999999</v>
+        <v>19.29072549999999</v>
       </c>
       <c r="O56">
-        <v>4.357666865999998</v>
+        <v>4.051052354999999</v>
       </c>
       <c r="P56">
-        <v>16.39312773399999</v>
+        <v>15.23967314499999</v>
       </c>
       <c r="Q56">
-        <v>44.69312773399999</v>
+        <v>43.53967314499999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1618853389962395</v>
+        <v>0.1641839433476201</v>
       </c>
       <c r="T56">
-        <v>1.957365586183076</v>
+        <v>1.996123357772033</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.21</v>
       </c>
       <c r="W56">
-        <v>0.050639</v>
+        <v>0.056801</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.024624718712339</v>
+        <v>2.647474017284332</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.105123324506429</v>
+        <v>0.1051068530745879</v>
       </c>
       <c r="C57">
-        <v>132.8339668435306</v>
+        <v>129.9025744629239</v>
       </c>
       <c r="D57">
-        <v>274.5889668435306</v>
+        <v>274.6185744629239</v>
       </c>
       <c r="E57">
-        <v>64.25500000000002</v>
+        <v>67.21600000000004</v>
       </c>
       <c r="F57">
-        <v>162.855</v>
+        <v>165.816</v>
       </c>
       <c r="G57">
         <v>21.1</v>
@@ -5961,28 +5961,28 @@
         <v>31</v>
       </c>
       <c r="M57">
-        <v>11.7092745</v>
+        <v>11.9221704</v>
       </c>
       <c r="N57">
-        <v>19.29072549999999</v>
+        <v>19.07782959999999</v>
       </c>
       <c r="O57">
-        <v>4.051052354999999</v>
+        <v>4.006344215999999</v>
       </c>
       <c r="P57">
-        <v>15.23967314499999</v>
+        <v>15.071485384</v>
       </c>
       <c r="Q57">
-        <v>43.53967314499999</v>
+        <v>43.371485384</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1641839433476201</v>
+        <v>0.1665870297149725</v>
       </c>
       <c r="T57">
-        <v>1.996123357772033</v>
+        <v>2.036642846251398</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.647474017284332</v>
+        <v>2.600197695547112</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1051068530745879</v>
+        <v>0.1050903816427467</v>
       </c>
       <c r="C58">
-        <v>129.9025744629239</v>
+        <v>126.9711884679028</v>
       </c>
       <c r="D58">
-        <v>274.6185744629239</v>
+        <v>274.6481884679028</v>
       </c>
       <c r="E58">
-        <v>67.21600000000004</v>
+        <v>70.17700000000005</v>
       </c>
       <c r="F58">
-        <v>165.816</v>
+        <v>168.777</v>
       </c>
       <c r="G58">
         <v>21.1</v>
@@ -6043,28 +6043,28 @@
         <v>31</v>
       </c>
       <c r="M58">
-        <v>11.9221704</v>
+        <v>12.1350663</v>
       </c>
       <c r="N58">
-        <v>19.07782959999999</v>
+        <v>18.86493369999999</v>
       </c>
       <c r="O58">
-        <v>4.006344215999999</v>
+        <v>3.961636076999999</v>
       </c>
       <c r="P58">
-        <v>15.071485384</v>
+        <v>14.903297623</v>
       </c>
       <c r="Q58">
-        <v>43.371485384</v>
+        <v>43.203297623</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1665870297149725</v>
+        <v>0.1691018875412715</v>
       </c>
       <c r="T58">
-        <v>2.036642846251398</v>
+        <v>2.079046962101896</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.600197695547112</v>
+        <v>2.554580192116461</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1050903816427467</v>
+        <v>0.1050739102109056</v>
       </c>
       <c r="C59">
-        <v>126.9711884679028</v>
+        <v>124.0398088605332</v>
       </c>
       <c r="D59">
-        <v>274.6481884679028</v>
+        <v>274.6778088605332</v>
       </c>
       <c r="E59">
-        <v>70.17700000000005</v>
+        <v>73.13800000000003</v>
       </c>
       <c r="F59">
-        <v>168.777</v>
+        <v>171.738</v>
       </c>
       <c r="G59">
         <v>21.1</v>
@@ -6125,28 +6125,28 @@
         <v>31</v>
       </c>
       <c r="M59">
-        <v>12.1350663</v>
+        <v>12.3479622</v>
       </c>
       <c r="N59">
-        <v>18.86493369999999</v>
+        <v>18.6520378</v>
       </c>
       <c r="O59">
-        <v>3.961636076999999</v>
+        <v>3.916927937999999</v>
       </c>
       <c r="P59">
-        <v>14.903297623</v>
+        <v>14.735109862</v>
       </c>
       <c r="Q59">
-        <v>43.203297623</v>
+        <v>43.035109862</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1691018875412715</v>
+        <v>0.1717365005021561</v>
       </c>
       <c r="T59">
-        <v>2.079046962101896</v>
+        <v>2.123470321564322</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.554580192116461</v>
+        <v>2.510535706045487</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1050739102109056</v>
+        <v>0.1068752287790644</v>
       </c>
       <c r="C60">
-        <v>124.0398088605331</v>
+        <v>117.8769323524612</v>
       </c>
       <c r="D60">
-        <v>274.6778088605331</v>
+        <v>271.4759323524612</v>
       </c>
       <c r="E60">
-        <v>73.13800000000001</v>
+        <v>76.09900000000002</v>
       </c>
       <c r="F60">
-        <v>171.738</v>
+        <v>174.699</v>
       </c>
       <c r="G60">
         <v>21.1</v>
@@ -6207,45 +6207,45 @@
         <v>31</v>
       </c>
       <c r="M60">
-        <v>12.3479622</v>
+        <v>13.2421842</v>
       </c>
       <c r="N60">
-        <v>18.6520378</v>
+        <v>17.7578158</v>
       </c>
       <c r="O60">
-        <v>3.916927937999999</v>
+        <v>3.729141317999999</v>
       </c>
       <c r="P60">
-        <v>14.735109862</v>
+        <v>14.028674482</v>
       </c>
       <c r="Q60">
-        <v>43.035109862</v>
+        <v>42.328674482</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1717365005021561</v>
+        <v>0.1744996311684498</v>
       </c>
       <c r="T60">
-        <v>2.123470321564321</v>
+        <v>2.170060674171256</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.21</v>
       </c>
       <c r="W60">
-        <v>0.056801</v>
+        <v>0.059882</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.510535706045488</v>
+        <v>2.341003533238874</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1068752287790644</v>
+        <v>0.1068895673472233</v>
       </c>
       <c r="C61">
-        <v>117.8769323524612</v>
+        <v>114.890744722737</v>
       </c>
       <c r="D61">
-        <v>271.4759323524612</v>
+        <v>271.4507447227369</v>
       </c>
       <c r="E61">
-        <v>76.09900000000002</v>
+        <v>79.06</v>
       </c>
       <c r="F61">
-        <v>174.699</v>
+        <v>177.66</v>
       </c>
       <c r="G61">
         <v>21.1</v>
@@ -6289,28 +6289,28 @@
         <v>31</v>
       </c>
       <c r="M61">
-        <v>13.2421842</v>
+        <v>13.466628</v>
       </c>
       <c r="N61">
-        <v>17.7578158</v>
+        <v>17.533372</v>
       </c>
       <c r="O61">
-        <v>3.729141317999999</v>
+        <v>3.682008119999999</v>
       </c>
       <c r="P61">
-        <v>14.028674482</v>
+        <v>13.85136388</v>
       </c>
       <c r="Q61">
-        <v>42.328674482</v>
+        <v>42.15136388</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1744996311684498</v>
+        <v>0.1774009183680581</v>
       </c>
       <c r="T61">
-        <v>2.170060674171256</v>
+        <v>2.218980544408537</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.341003533238874</v>
+        <v>2.301986807684893</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1068895673472233</v>
+        <v>0.1069039059153821</v>
       </c>
       <c r="C62">
-        <v>114.890744722737</v>
+        <v>111.9045617664129</v>
       </c>
       <c r="D62">
-        <v>271.4507447227369</v>
+        <v>271.4255617664129</v>
       </c>
       <c r="E62">
-        <v>79.06</v>
+        <v>82.02100000000002</v>
       </c>
       <c r="F62">
-        <v>177.66</v>
+        <v>180.621</v>
       </c>
       <c r="G62">
         <v>21.1</v>
@@ -6371,28 +6371,28 @@
         <v>31</v>
       </c>
       <c r="M62">
-        <v>13.466628</v>
+        <v>13.6910718</v>
       </c>
       <c r="N62">
-        <v>17.533372</v>
+        <v>17.3089282</v>
       </c>
       <c r="O62">
-        <v>3.682008119999999</v>
+        <v>3.634874921999999</v>
       </c>
       <c r="P62">
-        <v>13.85136388</v>
+        <v>13.674053278</v>
       </c>
       <c r="Q62">
-        <v>42.15136388</v>
+        <v>41.974053278</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1774009183680581</v>
+        <v>0.1804509895266208</v>
       </c>
       <c r="T62">
-        <v>2.218980544408537</v>
+        <v>2.270409125940038</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.301986807684893</v>
+        <v>2.264249319034321</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1069039059153821</v>
+        <v>0.106918244483541</v>
       </c>
       <c r="C63">
-        <v>111.9045617664129</v>
+        <v>108.9183834821884</v>
       </c>
       <c r="D63">
-        <v>271.4255617664129</v>
+        <v>271.4003834821884</v>
       </c>
       <c r="E63">
-        <v>82.02100000000002</v>
+        <v>84.98200000000003</v>
       </c>
       <c r="F63">
-        <v>180.621</v>
+        <v>183.582</v>
       </c>
       <c r="G63">
         <v>21.1</v>
@@ -6453,28 +6453,28 @@
         <v>31</v>
       </c>
       <c r="M63">
-        <v>13.6910718</v>
+        <v>13.9155156</v>
       </c>
       <c r="N63">
-        <v>17.3089282</v>
+        <v>17.08448439999999</v>
       </c>
       <c r="O63">
-        <v>3.634874921999999</v>
+        <v>3.587741723999998</v>
       </c>
       <c r="P63">
-        <v>13.674053278</v>
+        <v>13.49674267599999</v>
       </c>
       <c r="Q63">
-        <v>41.974053278</v>
+        <v>41.79674267599999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1804509895266208</v>
+        <v>0.1836615907461604</v>
       </c>
       <c r="T63">
-        <v>2.270409125940038</v>
+        <v>2.324544474920566</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.264249319034321</v>
+        <v>2.227729168727316</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.106918244483541</v>
+        <v>0.1069325830516998</v>
       </c>
       <c r="C64">
-        <v>108.9183834821884</v>
+        <v>105.9322098687635</v>
       </c>
       <c r="D64">
-        <v>271.4003834821884</v>
+        <v>271.3752098687635</v>
       </c>
       <c r="E64">
-        <v>84.98200000000003</v>
+        <v>87.94300000000001</v>
       </c>
       <c r="F64">
-        <v>183.582</v>
+        <v>186.543</v>
       </c>
       <c r="G64">
         <v>21.1</v>
@@ -6535,28 +6535,28 @@
         <v>31</v>
       </c>
       <c r="M64">
-        <v>13.9155156</v>
+        <v>14.1399594</v>
       </c>
       <c r="N64">
-        <v>17.08448439999999</v>
+        <v>16.86004059999999</v>
       </c>
       <c r="O64">
-        <v>3.587741723999998</v>
+        <v>3.540608525999999</v>
       </c>
       <c r="P64">
-        <v>13.49674267599999</v>
+        <v>13.31943207399999</v>
       </c>
       <c r="Q64">
-        <v>41.79674267599999</v>
+        <v>41.619432074</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1836615907461604</v>
+        <v>0.187045737977567</v>
       </c>
       <c r="T64">
-        <v>2.324544474920566</v>
+        <v>2.381606058981122</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.227729168727316</v>
+        <v>2.192368388271326</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1069325830516998</v>
+        <v>0.1069469216198586</v>
       </c>
       <c r="C65">
-        <v>105.9322098687635</v>
+        <v>102.9460409248385</v>
       </c>
       <c r="D65">
-        <v>271.3752098687635</v>
+        <v>271.3500409248385</v>
       </c>
       <c r="E65">
-        <v>87.94300000000001</v>
+        <v>90.90400000000002</v>
       </c>
       <c r="F65">
-        <v>186.543</v>
+        <v>189.504</v>
       </c>
       <c r="G65">
         <v>21.1</v>
@@ -6617,28 +6617,28 @@
         <v>31</v>
       </c>
       <c r="M65">
-        <v>14.1399594</v>
+        <v>14.3644032</v>
       </c>
       <c r="N65">
-        <v>16.86004059999999</v>
+        <v>16.63559679999999</v>
       </c>
       <c r="O65">
-        <v>3.540608525999999</v>
+        <v>3.493475327999999</v>
       </c>
       <c r="P65">
-        <v>13.31943207399999</v>
+        <v>13.142121472</v>
       </c>
       <c r="Q65">
-        <v>41.619432074</v>
+        <v>41.442121472</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.187045737977567</v>
+        <v>0.1906178933884962</v>
       </c>
       <c r="T65">
-        <v>2.381606058981122</v>
+        <v>2.441837731045042</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.192368388271326</v>
+        <v>2.158112632204587</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1069469216198586</v>
+        <v>0.1069612601880175</v>
       </c>
       <c r="C66">
-        <v>102.9460409248385</v>
+        <v>99.95987664911445</v>
       </c>
       <c r="D66">
-        <v>271.3500409248385</v>
+        <v>271.3248766491145</v>
       </c>
       <c r="E66">
-        <v>90.90400000000002</v>
+        <v>93.86500000000004</v>
       </c>
       <c r="F66">
-        <v>189.504</v>
+        <v>192.465</v>
       </c>
       <c r="G66">
         <v>21.1</v>
@@ -6699,28 +6699,28 @@
         <v>31</v>
       </c>
       <c r="M66">
-        <v>14.3644032</v>
+        <v>14.588847</v>
       </c>
       <c r="N66">
-        <v>16.63559679999999</v>
+        <v>16.41115299999999</v>
       </c>
       <c r="O66">
-        <v>3.493475327999999</v>
+        <v>3.446342129999998</v>
       </c>
       <c r="P66">
-        <v>13.142121472</v>
+        <v>12.96481086999999</v>
       </c>
       <c r="Q66">
-        <v>41.442121472</v>
+        <v>41.26481086999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1906178933884962</v>
+        <v>0.1943941719657643</v>
       </c>
       <c r="T66">
-        <v>2.441837731045042</v>
+        <v>2.505511212941187</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.158112632204587</v>
+        <v>2.124910899401439</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1069612601880175</v>
+        <v>0.1069755987561763</v>
       </c>
       <c r="C67">
-        <v>99.95987664911445</v>
+        <v>96.97371704029254</v>
       </c>
       <c r="D67">
-        <v>271.3248766491145</v>
+        <v>271.2997170402925</v>
       </c>
       <c r="E67">
-        <v>93.86500000000004</v>
+        <v>96.82600000000002</v>
       </c>
       <c r="F67">
-        <v>192.465</v>
+        <v>195.426</v>
       </c>
       <c r="G67">
         <v>21.1</v>
@@ -6781,28 +6781,28 @@
         <v>31</v>
       </c>
       <c r="M67">
-        <v>14.588847</v>
+        <v>14.8132908</v>
       </c>
       <c r="N67">
-        <v>16.41115299999999</v>
+        <v>16.1867092</v>
       </c>
       <c r="O67">
-        <v>3.446342129999998</v>
+        <v>3.399208931999999</v>
       </c>
       <c r="P67">
-        <v>12.96481086999999</v>
+        <v>12.787500268</v>
       </c>
       <c r="Q67">
-        <v>41.26481086999999</v>
+        <v>41.087500268</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1943941719657643</v>
+        <v>0.1983925845769892</v>
       </c>
       <c r="T67">
-        <v>2.505511212941187</v>
+        <v>2.572930193772398</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.124910899401439</v>
+        <v>2.092715279713539</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1069755987561763</v>
+        <v>0.1069899373243352</v>
       </c>
       <c r="C68">
-        <v>96.97371704029254</v>
+        <v>93.98756209707469</v>
       </c>
       <c r="D68">
-        <v>271.2997170402925</v>
+        <v>271.2745620970747</v>
       </c>
       <c r="E68">
-        <v>96.82600000000002</v>
+        <v>99.78700000000003</v>
       </c>
       <c r="F68">
-        <v>195.426</v>
+        <v>198.387</v>
       </c>
       <c r="G68">
         <v>21.1</v>
@@ -6863,28 +6863,28 @@
         <v>31</v>
       </c>
       <c r="M68">
-        <v>14.8132908</v>
+        <v>15.0377346</v>
       </c>
       <c r="N68">
-        <v>16.1867092</v>
+        <v>15.96226539999999</v>
       </c>
       <c r="O68">
-        <v>3.399208931999999</v>
+        <v>3.352075733999998</v>
       </c>
       <c r="P68">
-        <v>12.787500268</v>
+        <v>12.61018966599999</v>
       </c>
       <c r="Q68">
-        <v>41.087500268</v>
+        <v>40.91018966599999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1983925845769892</v>
+        <v>0.2026333252252581</v>
       </c>
       <c r="T68">
-        <v>2.572930193772398</v>
+        <v>2.644435173441865</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.092715279713539</v>
+        <v>2.061480723299904</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1069899373243352</v>
+        <v>0.107004275892494</v>
       </c>
       <c r="C69">
-        <v>93.98756209707469</v>
+        <v>91.00141181816323</v>
       </c>
       <c r="D69">
-        <v>271.2745620970747</v>
+        <v>271.2494118181633</v>
       </c>
       <c r="E69">
-        <v>99.78700000000003</v>
+        <v>102.748</v>
       </c>
       <c r="F69">
-        <v>198.387</v>
+        <v>201.348</v>
       </c>
       <c r="G69">
         <v>21.1</v>
@@ -6945,28 +6945,28 @@
         <v>31</v>
       </c>
       <c r="M69">
-        <v>15.0377346</v>
+        <v>15.26217840000001</v>
       </c>
       <c r="N69">
-        <v>15.96226539999999</v>
+        <v>15.73782159999999</v>
       </c>
       <c r="O69">
-        <v>3.352075733999998</v>
+        <v>3.304942535999998</v>
       </c>
       <c r="P69">
-        <v>12.61018966599999</v>
+        <v>12.43287906399999</v>
       </c>
       <c r="Q69">
-        <v>40.91018966599999</v>
+        <v>40.732879064</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2026333252252581</v>
+        <v>0.2071391121640438</v>
       </c>
       <c r="T69">
-        <v>2.644435173441865</v>
+        <v>2.720409214340673</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.061480723299904</v>
+        <v>2.031164830310199</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.107004275892494</v>
+        <v>0.1070186144606529</v>
       </c>
       <c r="C70">
-        <v>91.00141181816323</v>
+        <v>88.0152662022611</v>
       </c>
       <c r="D70">
-        <v>271.2494118181633</v>
+        <v>271.2242662022611</v>
       </c>
       <c r="E70">
-        <v>102.748</v>
+        <v>105.709</v>
       </c>
       <c r="F70">
-        <v>201.348</v>
+        <v>204.309</v>
       </c>
       <c r="G70">
         <v>21.1</v>
@@ -7027,28 +7027,28 @@
         <v>31</v>
       </c>
       <c r="M70">
-        <v>15.26217840000001</v>
+        <v>15.4866222</v>
       </c>
       <c r="N70">
-        <v>15.73782159999999</v>
+        <v>15.51337779999999</v>
       </c>
       <c r="O70">
-        <v>3.304942535999998</v>
+        <v>3.257809337999999</v>
       </c>
       <c r="P70">
-        <v>12.43287906399999</v>
+        <v>12.255568462</v>
       </c>
       <c r="Q70">
-        <v>40.732879064</v>
+        <v>40.555568462</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2071391121640438</v>
+        <v>0.2119355950343641</v>
       </c>
       <c r="T70">
-        <v>2.720409214340673</v>
+        <v>2.801284806265211</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.031164830310199</v>
+        <v>2.001727658856428</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1070186144606529</v>
+        <v>0.1148855530288117</v>
       </c>
       <c r="C71">
-        <v>88.0152662022611</v>
+        <v>71.92693929742404</v>
       </c>
       <c r="D71">
-        <v>271.2242662022611</v>
+        <v>258.0969392974241</v>
       </c>
       <c r="E71">
-        <v>105.709</v>
+        <v>108.67</v>
       </c>
       <c r="F71">
-        <v>204.309</v>
+        <v>207.27</v>
       </c>
       <c r="G71">
         <v>21.1</v>
@@ -7109,45 +7109,45 @@
         <v>31</v>
       </c>
       <c r="M71">
-        <v>15.4866222</v>
+        <v>18.6543</v>
       </c>
       <c r="N71">
-        <v>15.51337779999999</v>
+        <v>12.34569999999999</v>
       </c>
       <c r="O71">
-        <v>3.257809337999999</v>
+        <v>2.592596999999999</v>
       </c>
       <c r="P71">
-        <v>12.255568462</v>
+        <v>9.753102999999996</v>
       </c>
       <c r="Q71">
-        <v>40.555568462</v>
+        <v>38.05310299999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2119355950343641</v>
+        <v>0.2170518434293724</v>
       </c>
       <c r="T71">
-        <v>2.801284806265211</v>
+        <v>2.887552104318051</v>
       </c>
       <c r="U71">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V71">
         <v>0.21</v>
       </c>
       <c r="W71">
-        <v>0.059882</v>
+        <v>0.0711</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.001727658856428</v>
+        <v>1.661815238309665</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1148855530288117</v>
+        <v>0.1150120715969706</v>
       </c>
       <c r="C72">
-        <v>71.92693929742404</v>
+        <v>68.76519593088392</v>
       </c>
       <c r="D72">
-        <v>258.0969392974241</v>
+        <v>257.8961959308839</v>
       </c>
       <c r="E72">
-        <v>108.67</v>
+        <v>111.6310000000001</v>
       </c>
       <c r="F72">
-        <v>207.27</v>
+        <v>210.2310000000001</v>
       </c>
       <c r="G72">
         <v>21.1</v>
@@ -7191,28 +7191,28 @@
         <v>31</v>
       </c>
       <c r="M72">
-        <v>18.6543</v>
+        <v>18.92079</v>
       </c>
       <c r="N72">
-        <v>12.34569999999999</v>
+        <v>12.07920999999999</v>
       </c>
       <c r="O72">
-        <v>2.592596999999999</v>
+        <v>2.536634099999998</v>
       </c>
       <c r="P72">
-        <v>9.753102999999996</v>
+        <v>9.542575899999994</v>
       </c>
       <c r="Q72">
-        <v>38.05310299999999</v>
+        <v>37.84257589999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2170518434293724</v>
+        <v>0.2225209365412779</v>
       </c>
       <c r="T72">
-        <v>2.887552104318051</v>
+        <v>2.979768871202123</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.661815238309665</v>
+        <v>1.638409389882769</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1150120715969706</v>
+        <v>0.1151385901651294</v>
       </c>
       <c r="C73">
-        <v>68.76519593088398</v>
+        <v>65.6037645911403</v>
       </c>
       <c r="D73">
-        <v>257.8961959308839</v>
+        <v>257.6957645911403</v>
       </c>
       <c r="E73">
-        <v>111.631</v>
+        <v>114.592</v>
       </c>
       <c r="F73">
-        <v>210.231</v>
+        <v>213.192</v>
       </c>
       <c r="G73">
         <v>21.1</v>
@@ -7273,28 +7273,28 @@
         <v>31</v>
       </c>
       <c r="M73">
-        <v>18.92079</v>
+        <v>19.18728</v>
       </c>
       <c r="N73">
-        <v>12.07921</v>
+        <v>11.81272</v>
       </c>
       <c r="O73">
-        <v>2.536634099999999</v>
+        <v>2.480671199999999</v>
       </c>
       <c r="P73">
-        <v>9.542575899999997</v>
+        <v>9.332048799999995</v>
       </c>
       <c r="Q73">
-        <v>37.8425759</v>
+        <v>37.63204879999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2225209365412778</v>
+        <v>0.2283806791611764</v>
       </c>
       <c r="T73">
-        <v>2.979768871202122</v>
+        <v>3.078572550006483</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.638409389882769</v>
+        <v>1.615653703912175</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1151385901651294</v>
+        <v>0.1152651087332882</v>
       </c>
       <c r="C74">
-        <v>65.6037645911403</v>
+        <v>62.44264455125642</v>
       </c>
       <c r="D74">
-        <v>257.6957645911403</v>
+        <v>257.4956445512564</v>
       </c>
       <c r="E74">
-        <v>114.592</v>
+        <v>117.553</v>
       </c>
       <c r="F74">
-        <v>213.192</v>
+        <v>216.153</v>
       </c>
       <c r="G74">
         <v>21.1</v>
@@ -7355,28 +7355,28 @@
         <v>31</v>
       </c>
       <c r="M74">
-        <v>19.18728</v>
+        <v>19.45377</v>
       </c>
       <c r="N74">
-        <v>11.81272</v>
+        <v>11.54622999999999</v>
       </c>
       <c r="O74">
-        <v>2.480671199999999</v>
+        <v>2.424708299999998</v>
       </c>
       <c r="P74">
-        <v>9.332048799999995</v>
+        <v>9.121521699999995</v>
       </c>
       <c r="Q74">
-        <v>37.63204879999999</v>
+        <v>37.4215217</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2283806791611764</v>
+        <v>0.2346744767899565</v>
       </c>
       <c r="T74">
-        <v>3.078572550006483</v>
+        <v>3.18469501983339</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.615653703912175</v>
+        <v>1.59352146139283</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1152651087332882</v>
+        <v>0.1153916273014471</v>
       </c>
       <c r="C75">
-        <v>62.44264455125642</v>
+        <v>59.28183508655238</v>
       </c>
       <c r="D75">
-        <v>257.4956445512564</v>
+        <v>257.2958350865524</v>
       </c>
       <c r="E75">
-        <v>117.553</v>
+        <v>120.514</v>
       </c>
       <c r="F75">
-        <v>216.153</v>
+        <v>219.114</v>
       </c>
       <c r="G75">
         <v>21.1</v>
@@ -7437,28 +7437,28 @@
         <v>31</v>
       </c>
       <c r="M75">
-        <v>19.45377</v>
+        <v>19.72026</v>
       </c>
       <c r="N75">
-        <v>11.54622999999999</v>
+        <v>11.27974</v>
       </c>
       <c r="O75">
-        <v>2.424708299999998</v>
+        <v>2.368745399999999</v>
       </c>
       <c r="P75">
-        <v>9.121521699999995</v>
+        <v>8.910994599999997</v>
       </c>
       <c r="Q75">
-        <v>37.4215217</v>
+        <v>37.2109946</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2346744767899565</v>
+        <v>0.2414524126978734</v>
       </c>
       <c r="T75">
-        <v>3.18469501983339</v>
+        <v>3.298980756570059</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.59352146139283</v>
+        <v>1.571987387590224</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1153916273014471</v>
+        <v>0.1155181458696059</v>
       </c>
       <c r="C76">
-        <v>59.28183508655238</v>
+        <v>56.1213354745955</v>
       </c>
       <c r="D76">
-        <v>257.2958350865524</v>
+        <v>257.0963354745955</v>
       </c>
       <c r="E76">
-        <v>120.514</v>
+        <v>123.475</v>
       </c>
       <c r="F76">
-        <v>219.114</v>
+        <v>222.075</v>
       </c>
       <c r="G76">
         <v>21.1</v>
@@ -7519,28 +7519,28 @@
         <v>31</v>
       </c>
       <c r="M76">
-        <v>19.72026</v>
+        <v>19.98675</v>
       </c>
       <c r="N76">
-        <v>11.27974</v>
+        <v>11.01325</v>
       </c>
       <c r="O76">
-        <v>2.368745399999999</v>
+        <v>2.312782499999999</v>
       </c>
       <c r="P76">
-        <v>8.910994599999997</v>
+        <v>8.700467499999997</v>
       </c>
       <c r="Q76">
-        <v>37.2109946</v>
+        <v>37.0004675</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2414524126978734</v>
+        <v>0.2487725834784238</v>
       </c>
       <c r="T76">
-        <v>3.298980756570059</v>
+        <v>3.422409352245662</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.571987387590224</v>
+        <v>1.551027555755688</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1155181458696059</v>
+        <v>0.1156446644377648</v>
       </c>
       <c r="C77">
-        <v>56.1213354745955</v>
+        <v>52.96114499519214</v>
       </c>
       <c r="D77">
-        <v>257.0963354745955</v>
+        <v>256.8971449951921</v>
       </c>
       <c r="E77">
-        <v>123.475</v>
+        <v>126.436</v>
       </c>
       <c r="F77">
-        <v>222.075</v>
+        <v>225.036</v>
       </c>
       <c r="G77">
         <v>21.1</v>
@@ -7601,28 +7601,28 @@
         <v>31</v>
       </c>
       <c r="M77">
-        <v>19.98675</v>
+        <v>20.25324</v>
       </c>
       <c r="N77">
-        <v>11.01325</v>
+        <v>10.74675999999999</v>
       </c>
       <c r="O77">
-        <v>2.312782499999999</v>
+        <v>2.256819599999999</v>
       </c>
       <c r="P77">
-        <v>8.700467499999997</v>
+        <v>8.489940399999997</v>
       </c>
       <c r="Q77">
-        <v>37.0004675</v>
+        <v>36.7899404</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2487725834784238</v>
+        <v>0.2567027684906866</v>
       </c>
       <c r="T77">
-        <v>3.422409352245662</v>
+        <v>3.556123664227565</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.551027555755688</v>
+        <v>1.530619298443113</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1156446644377648</v>
+        <v>0.1157711830059236</v>
       </c>
       <c r="C78">
-        <v>52.96114499519214</v>
+        <v>49.80126293037893</v>
       </c>
       <c r="D78">
-        <v>256.8971449951921</v>
+        <v>256.6982629303789</v>
       </c>
       <c r="E78">
-        <v>126.436</v>
+        <v>129.397</v>
       </c>
       <c r="F78">
-        <v>225.036</v>
+        <v>227.997</v>
       </c>
       <c r="G78">
         <v>21.1</v>
@@ -7683,28 +7683,28 @@
         <v>31</v>
       </c>
       <c r="M78">
-        <v>20.25324</v>
+        <v>20.51973</v>
       </c>
       <c r="N78">
-        <v>10.74675999999999</v>
+        <v>10.48027</v>
       </c>
       <c r="O78">
-        <v>2.256819599999999</v>
+        <v>2.200856699999999</v>
       </c>
       <c r="P78">
-        <v>8.489940399999997</v>
+        <v>8.279413299999998</v>
       </c>
       <c r="Q78">
-        <v>36.7899404</v>
+        <v>36.5794133</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2567027684906866</v>
+        <v>0.2653225348083637</v>
       </c>
       <c r="T78">
-        <v>3.556123664227565</v>
+        <v>3.701465307686155</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.530619298443113</v>
+        <v>1.51074112573606</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1157711830059236</v>
+        <v>0.1538030748754265</v>
       </c>
       <c r="C79">
-        <v>49.80126293037893</v>
+        <v>-1.620382135568576</v>
       </c>
       <c r="D79">
-        <v>256.6982629303789</v>
+        <v>208.2376178644315</v>
       </c>
       <c r="E79">
-        <v>129.397</v>
+        <v>132.358</v>
       </c>
       <c r="F79">
-        <v>227.997</v>
+        <v>230.958</v>
       </c>
       <c r="G79">
         <v>21.1</v>
@@ -7765,45 +7765,45 @@
         <v>31</v>
       </c>
       <c r="M79">
-        <v>20.51973</v>
+        <v>33.90463440000001</v>
       </c>
       <c r="N79">
-        <v>10.48027</v>
+        <v>-2.90463440000001</v>
       </c>
       <c r="O79">
-        <v>2.200856699999999</v>
+        <v>-0.609973224000002</v>
       </c>
       <c r="P79">
-        <v>8.279413299999998</v>
+        <v>-2.294661176000008</v>
       </c>
       <c r="Q79">
-        <v>36.5794133</v>
+        <v>26.00533882399999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2653225348083637</v>
+        <v>0.2785676839921065</v>
       </c>
       <c r="T79">
-        <v>3.701465307686155</v>
+        <v>3.92479755119159</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.21</v>
+        <v>0.1920091490501369</v>
       </c>
       <c r="W79">
-        <v>0.0711</v>
+        <v>0.1186130569194399</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.51074112573606</v>
+        <v>0.914329281191128</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1538030748754265</v>
+        <v>0.1548130748754266</v>
       </c>
       <c r="C80">
-        <v>-1.620382135568576</v>
+        <v>-5.620170324832173</v>
       </c>
       <c r="D80">
-        <v>208.2376178644315</v>
+        <v>207.1988296751679</v>
       </c>
       <c r="E80">
-        <v>132.358</v>
+        <v>135.319</v>
       </c>
       <c r="F80">
-        <v>230.958</v>
+        <v>233.919</v>
       </c>
       <c r="G80">
         <v>21.1</v>
@@ -7847,37 +7847,37 @@
         <v>31</v>
       </c>
       <c r="M80">
-        <v>33.90463440000001</v>
+        <v>34.33930920000001</v>
       </c>
       <c r="N80">
-        <v>-2.90463440000001</v>
+        <v>-3.339309200000013</v>
       </c>
       <c r="O80">
-        <v>-0.609973224000002</v>
+        <v>-0.7012549320000028</v>
       </c>
       <c r="P80">
-        <v>-2.294661176000008</v>
+        <v>-2.63805426800001</v>
       </c>
       <c r="Q80">
-        <v>26.00533882399999</v>
+        <v>25.66194573199999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2785676839921065</v>
+        <v>0.2896518594203021</v>
       </c>
       <c r="T80">
-        <v>3.92479755119159</v>
+        <v>4.111692672676904</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1920091490501369</v>
+        <v>0.1895786534925402</v>
       </c>
       <c r="W80">
-        <v>0.1186130569194399</v>
+        <v>0.1189698536672951</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.914329281191128</v>
+        <v>0.9027554928216199</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1548130748754266</v>
+        <v>0.1558230748754266</v>
       </c>
       <c r="C81">
-        <v>-5.620170324832173</v>
+        <v>-9.609646019510251</v>
       </c>
       <c r="D81">
-        <v>207.1988296751679</v>
+        <v>206.1703539804898</v>
       </c>
       <c r="E81">
-        <v>135.319</v>
+        <v>138.28</v>
       </c>
       <c r="F81">
-        <v>233.919</v>
+        <v>236.88</v>
       </c>
       <c r="G81">
         <v>21.1</v>
@@ -7929,37 +7929,37 @@
         <v>31</v>
       </c>
       <c r="M81">
-        <v>34.33930920000001</v>
+        <v>34.77398400000001</v>
       </c>
       <c r="N81">
-        <v>-3.339309200000013</v>
+        <v>-3.773984000000009</v>
       </c>
       <c r="O81">
-        <v>-0.7012549320000028</v>
+        <v>-0.7925366400000019</v>
       </c>
       <c r="P81">
-        <v>-2.63805426800001</v>
+        <v>-2.981447360000007</v>
       </c>
       <c r="Q81">
-        <v>25.66194573199999</v>
+        <v>25.31855263999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2896518594203021</v>
+        <v>0.3018444523913172</v>
       </c>
       <c r="T81">
-        <v>4.111692672676904</v>
+        <v>4.317277306310749</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1895786534925402</v>
+        <v>0.1872089203238834</v>
       </c>
       <c r="W81">
-        <v>0.1189698536672951</v>
+        <v>0.1193177304964539</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9027554928216199</v>
+        <v>0.8914710491613498</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1558230748754266</v>
+        <v>0.1568330748754266</v>
       </c>
       <c r="C82">
-        <v>-9.609646019510251</v>
+        <v>-13.58896202593164</v>
       </c>
       <c r="D82">
-        <v>206.1703539804898</v>
+        <v>205.1520379740684</v>
       </c>
       <c r="E82">
-        <v>138.28</v>
+        <v>141.241</v>
       </c>
       <c r="F82">
-        <v>236.88</v>
+        <v>239.841</v>
       </c>
       <c r="G82">
         <v>21.1</v>
@@ -8011,37 +8011,37 @@
         <v>31</v>
       </c>
       <c r="M82">
-        <v>34.77398400000001</v>
+        <v>35.20865880000001</v>
       </c>
       <c r="N82">
-        <v>-3.773984000000009</v>
+        <v>-4.208658800000013</v>
       </c>
       <c r="O82">
-        <v>-0.7925366400000019</v>
+        <v>-0.8838183480000026</v>
       </c>
       <c r="P82">
-        <v>-2.981447360000007</v>
+        <v>-3.32484045200001</v>
       </c>
       <c r="Q82">
-        <v>25.31855263999999</v>
+        <v>24.97515954799999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3018444523913172</v>
+        <v>0.3153204762013865</v>
       </c>
       <c r="T82">
-        <v>4.317277306310749</v>
+        <v>4.544502427695526</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1872089203238834</v>
+        <v>0.184897699085317</v>
       </c>
       <c r="W82">
-        <v>0.1193177304964539</v>
+        <v>0.1196570177742755</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8914710491613498</v>
+        <v>0.8804652337396046</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1568330748754266</v>
+        <v>0.1578430748754266</v>
       </c>
       <c r="C83">
-        <v>-13.58896202593164</v>
+        <v>-17.55826814630083</v>
       </c>
       <c r="D83">
-        <v>205.1520379740684</v>
+        <v>204.1437318536992</v>
       </c>
       <c r="E83">
-        <v>141.241</v>
+        <v>144.2020000000001</v>
       </c>
       <c r="F83">
-        <v>239.841</v>
+        <v>242.802</v>
       </c>
       <c r="G83">
         <v>21.1</v>
@@ -8093,37 +8093,37 @@
         <v>31</v>
       </c>
       <c r="M83">
-        <v>35.20865880000001</v>
+        <v>35.64333360000001</v>
       </c>
       <c r="N83">
-        <v>-4.208658800000013</v>
+        <v>-4.643333600000016</v>
       </c>
       <c r="O83">
-        <v>-0.8838183480000026</v>
+        <v>-0.9751000560000034</v>
       </c>
       <c r="P83">
-        <v>-3.32484045200001</v>
+        <v>-3.668233544000013</v>
       </c>
       <c r="Q83">
-        <v>24.97515954799999</v>
+        <v>24.63176645599999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3153204762013865</v>
+        <v>0.3302938359903524</v>
       </c>
       <c r="T83">
-        <v>4.544502427695526</v>
+        <v>4.796974784789722</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.184897699085317</v>
+        <v>0.1826428490964716</v>
       </c>
       <c r="W83">
-        <v>0.1196570177742755</v>
+        <v>0.119988029752638</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8804652337396046</v>
+        <v>0.8697278528403412</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1578430748754266</v>
+        <v>0.1588530748754266</v>
       </c>
       <c r="C84">
-        <v>-17.55826814630083</v>
+        <v>-21.51771125216223</v>
       </c>
       <c r="D84">
-        <v>204.1437318536992</v>
+        <v>203.1452887478378</v>
       </c>
       <c r="E84">
-        <v>144.2020000000001</v>
+        <v>147.163</v>
       </c>
       <c r="F84">
-        <v>242.802</v>
+        <v>245.763</v>
       </c>
       <c r="G84">
         <v>21.1</v>
@@ -8175,37 +8175,37 @@
         <v>31</v>
       </c>
       <c r="M84">
-        <v>35.64333360000001</v>
+        <v>36.07800840000001</v>
       </c>
       <c r="N84">
-        <v>-4.643333600000016</v>
+        <v>-5.078008400000012</v>
       </c>
       <c r="O84">
-        <v>-0.9751000560000034</v>
+        <v>-1.066381764000003</v>
       </c>
       <c r="P84">
-        <v>-3.668233544000013</v>
+        <v>-4.01162663600001</v>
       </c>
       <c r="Q84">
-        <v>24.63176645599999</v>
+        <v>24.28837336399999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3302938359903524</v>
+        <v>0.3470287675191967</v>
       </c>
       <c r="T84">
-        <v>4.796974784789722</v>
+        <v>5.079149772130294</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1826428490964716</v>
+        <v>0.1804423328422973</v>
       </c>
       <c r="W84">
-        <v>0.119988029752638</v>
+        <v>0.1203110655387508</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8697278528403412</v>
+        <v>0.8592492040109395</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1588530748754266</v>
+        <v>0.1598630748754266</v>
       </c>
       <c r="C85">
-        <v>-21.51771125216223</v>
+        <v>-25.46743535571861</v>
       </c>
       <c r="D85">
-        <v>203.1452887478378</v>
+        <v>202.1565646442814</v>
       </c>
       <c r="E85">
-        <v>147.163</v>
+        <v>150.1240000000001</v>
       </c>
       <c r="F85">
-        <v>245.763</v>
+        <v>248.724</v>
       </c>
       <c r="G85">
         <v>21.1</v>
@@ -8257,37 +8257,37 @@
         <v>31</v>
       </c>
       <c r="M85">
-        <v>36.07800840000001</v>
+        <v>36.51268320000001</v>
       </c>
       <c r="N85">
-        <v>-5.078008400000012</v>
+        <v>-5.512683200000016</v>
       </c>
       <c r="O85">
-        <v>-1.066381764000003</v>
+        <v>-1.157663472000003</v>
       </c>
       <c r="P85">
-        <v>-4.01162663600001</v>
+        <v>-4.355019728000013</v>
       </c>
       <c r="Q85">
-        <v>24.28837336399999</v>
+        <v>23.94498027199999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3470287675191967</v>
+        <v>0.3658555654891466</v>
       </c>
       <c r="T85">
-        <v>5.079149772130294</v>
+        <v>5.396596632888438</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1804423328422973</v>
+        <v>0.1782942098322699</v>
       </c>
       <c r="W85">
-        <v>0.1203110655387508</v>
+        <v>0.1206264099966228</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8592492040109395</v>
+        <v>0.8490200468203331</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1598630748754266</v>
+        <v>0.1608730748754266</v>
       </c>
       <c r="C86">
-        <v>-25.46743535571858</v>
+        <v>-29.40758167907751</v>
       </c>
       <c r="D86">
-        <v>202.1565646442814</v>
+        <v>201.1774183209225</v>
       </c>
       <c r="E86">
-        <v>150.124</v>
+        <v>153.085</v>
       </c>
       <c r="F86">
-        <v>248.724</v>
+        <v>251.685</v>
       </c>
       <c r="G86">
         <v>21.1</v>
@@ -8339,37 +8339,37 @@
         <v>31</v>
       </c>
       <c r="M86">
-        <v>36.51268320000001</v>
+        <v>36.947358</v>
       </c>
       <c r="N86">
-        <v>-5.512683200000009</v>
+        <v>-5.947358000000005</v>
       </c>
       <c r="O86">
-        <v>-1.157663472000002</v>
+        <v>-1.248945180000001</v>
       </c>
       <c r="P86">
-        <v>-4.355019728000006</v>
+        <v>-4.698412820000004</v>
       </c>
       <c r="Q86">
-        <v>23.944980272</v>
+        <v>23.60158718</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3658555654891464</v>
+        <v>0.3871926031884228</v>
       </c>
       <c r="T86">
-        <v>5.396596632888435</v>
+        <v>5.756369741747664</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.17829420983227</v>
+        <v>0.1761966308930668</v>
       </c>
       <c r="W86">
-        <v>0.1206264099966228</v>
+        <v>0.1209343345848978</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8490200468203332</v>
+        <v>0.8390315756812705</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1608730748754266</v>
+        <v>0.1618830748754266</v>
       </c>
       <c r="C87">
-        <v>-29.40758167907751</v>
+        <v>-33.33828872149488</v>
       </c>
       <c r="D87">
-        <v>201.1774183209225</v>
+        <v>200.2077112785051</v>
       </c>
       <c r="E87">
-        <v>153.085</v>
+        <v>156.046</v>
       </c>
       <c r="F87">
-        <v>251.685</v>
+        <v>254.646</v>
       </c>
       <c r="G87">
         <v>21.1</v>
@@ -8421,37 +8421,37 @@
         <v>31</v>
       </c>
       <c r="M87">
-        <v>36.947358</v>
+        <v>37.3820328</v>
       </c>
       <c r="N87">
-        <v>-5.947358000000005</v>
+        <v>-6.382032800000008</v>
       </c>
       <c r="O87">
-        <v>-1.248945180000001</v>
+        <v>-1.340226888000002</v>
       </c>
       <c r="P87">
-        <v>-4.698412820000004</v>
+        <v>-5.041805912000006</v>
       </c>
       <c r="Q87">
-        <v>23.60158718</v>
+        <v>23.258194088</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3871926031884228</v>
+        <v>0.4115777891304531</v>
       </c>
       <c r="T87">
-        <v>5.756369741747664</v>
+        <v>6.167539009015355</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1761966308930668</v>
+        <v>0.1741478328594265</v>
       </c>
       <c r="W87">
-        <v>0.1209343345848978</v>
+        <v>0.1212350981362362</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8390315756812705</v>
+        <v>0.8292753945686975</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1618830748754266</v>
+        <v>0.1628930748754266</v>
       </c>
       <c r="C88">
-        <v>-33.33828872149488</v>
+        <v>-37.25969232468279</v>
       </c>
       <c r="D88">
-        <v>200.2077112785051</v>
+        <v>199.2473076753172</v>
       </c>
       <c r="E88">
-        <v>156.046</v>
+        <v>159.007</v>
       </c>
       <c r="F88">
-        <v>254.646</v>
+        <v>257.607</v>
       </c>
       <c r="G88">
         <v>21.1</v>
@@ -8503,37 +8503,37 @@
         <v>31</v>
       </c>
       <c r="M88">
-        <v>37.3820328</v>
+        <v>37.81670760000001</v>
       </c>
       <c r="N88">
-        <v>-6.382032800000008</v>
+        <v>-6.816707600000012</v>
       </c>
       <c r="O88">
-        <v>-1.340226888000002</v>
+        <v>-1.431508596000002</v>
       </c>
       <c r="P88">
-        <v>-5.041805912000006</v>
+        <v>-5.385199004000009</v>
       </c>
       <c r="Q88">
-        <v>23.258194088</v>
+        <v>22.91480099599999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4115777891304531</v>
+        <v>0.4397145421404879</v>
       </c>
       <c r="T88">
-        <v>6.167539009015355</v>
+        <v>6.641965086631921</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1741478328594265</v>
+        <v>0.1721461336311572</v>
       </c>
       <c r="W88">
-        <v>0.1212350981362362</v>
+        <v>0.1215289475829461</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8292753945686975</v>
+        <v>0.8197434934817009</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1628930748754266</v>
+        <v>0.1639030748754266</v>
       </c>
       <c r="C89">
-        <v>-37.25969232468279</v>
+        <v>-41.17192573624706</v>
       </c>
       <c r="D89">
-        <v>199.2473076753172</v>
+        <v>198.296074263753</v>
       </c>
       <c r="E89">
-        <v>159.007</v>
+        <v>161.968</v>
       </c>
       <c r="F89">
-        <v>257.607</v>
+        <v>260.568</v>
       </c>
       <c r="G89">
         <v>21.1</v>
@@ -8585,37 +8585,37 @@
         <v>31</v>
       </c>
       <c r="M89">
-        <v>37.81670760000001</v>
+        <v>38.25138240000001</v>
       </c>
       <c r="N89">
-        <v>-6.816707600000012</v>
+        <v>-7.251382400000015</v>
       </c>
       <c r="O89">
-        <v>-1.431508596000002</v>
+        <v>-1.522790304000003</v>
       </c>
       <c r="P89">
-        <v>-5.385199004000009</v>
+        <v>-5.728592096000012</v>
       </c>
       <c r="Q89">
-        <v>22.91480099599999</v>
+        <v>22.57140790399999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4397145421404879</v>
+        <v>0.4725407539855286</v>
       </c>
       <c r="T89">
-        <v>6.641965086631921</v>
+        <v>7.195462177184582</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1721461336311572</v>
+        <v>0.1701899275671667</v>
       </c>
       <c r="W89">
-        <v>0.1215289475829461</v>
+        <v>0.1218161186331399</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8197434934817009</v>
+        <v>0.8104282265103179</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1639030748754266</v>
+        <v>0.1649130748754266</v>
       </c>
       <c r="C90">
-        <v>-41.17192573624706</v>
+        <v>-45.07511967131592</v>
       </c>
       <c r="D90">
-        <v>198.296074263753</v>
+        <v>197.3538803286841</v>
       </c>
       <c r="E90">
-        <v>161.968</v>
+        <v>164.929</v>
       </c>
       <c r="F90">
-        <v>260.568</v>
+        <v>263.529</v>
       </c>
       <c r="G90">
         <v>21.1</v>
@@ -8667,37 +8667,37 @@
         <v>31</v>
       </c>
       <c r="M90">
-        <v>38.25138240000001</v>
+        <v>38.6860572</v>
       </c>
       <c r="N90">
-        <v>-7.251382400000015</v>
+        <v>-7.686057200000004</v>
       </c>
       <c r="O90">
-        <v>-1.522790304000003</v>
+        <v>-1.614072012000001</v>
       </c>
       <c r="P90">
-        <v>-5.728592096000012</v>
+        <v>-6.071985188000003</v>
       </c>
       <c r="Q90">
-        <v>22.57140790399999</v>
+        <v>22.228014812</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4725407539855286</v>
+        <v>0.511335367984213</v>
       </c>
       <c r="T90">
-        <v>7.195462177184582</v>
+        <v>7.84959510238318</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1701899275671667</v>
+        <v>0.1682776811900076</v>
       </c>
       <c r="W90">
-        <v>0.1218161186331399</v>
+        <v>0.1220968364013069</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8104282265103179</v>
+        <v>0.8013222913809888</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1649130748754266</v>
+        <v>0.216948869646787</v>
       </c>
       <c r="C91">
-        <v>-45.07511967131592</v>
+        <v>-86.84704195197142</v>
       </c>
       <c r="D91">
-        <v>197.3538803286841</v>
+        <v>158.5429580480286</v>
       </c>
       <c r="E91">
-        <v>164.929</v>
+        <v>167.89</v>
       </c>
       <c r="F91">
-        <v>263.529</v>
+        <v>266.49</v>
       </c>
       <c r="G91">
         <v>21.1</v>
@@ -8749,45 +8749,45 @@
         <v>31</v>
       </c>
       <c r="M91">
-        <v>38.6860572</v>
+        <v>53.511192</v>
       </c>
       <c r="N91">
-        <v>-7.686057200000004</v>
+        <v>-22.511192</v>
       </c>
       <c r="O91">
-        <v>-1.614072012000001</v>
+        <v>-4.727350320000001</v>
       </c>
       <c r="P91">
-        <v>-6.071985188000003</v>
+        <v>-17.78384168</v>
       </c>
       <c r="Q91">
-        <v>22.228014812</v>
+        <v>10.51615832</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.511335367984213</v>
+        <v>0.5821468524962384</v>
       </c>
       <c r="T91">
-        <v>7.84959510238318</v>
+        <v>9.043578460564737</v>
       </c>
       <c r="U91">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1682776811900076</v>
+        <v>0.1216567928443829</v>
       </c>
       <c r="W91">
-        <v>0.1220968364013069</v>
+        <v>0.1763713159968479</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8013222913809888</v>
+        <v>0.5793180611637281</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.216948869646787</v>
+        <v>0.2184988696467869</v>
       </c>
       <c r="C92">
-        <v>-86.84704195197142</v>
+        <v>-90.73135324877254</v>
       </c>
       <c r="D92">
-        <v>158.5429580480286</v>
+        <v>157.6196467512275</v>
       </c>
       <c r="E92">
-        <v>167.89</v>
+        <v>170.851</v>
       </c>
       <c r="F92">
-        <v>266.49</v>
+        <v>269.451</v>
       </c>
       <c r="G92">
         <v>21.1</v>
@@ -8831,37 +8831,37 @@
         <v>31</v>
       </c>
       <c r="M92">
-        <v>53.511192</v>
+        <v>54.10576080000001</v>
       </c>
       <c r="N92">
-        <v>-22.511192</v>
+        <v>-23.10576080000001</v>
       </c>
       <c r="O92">
-        <v>-4.727350320000001</v>
+        <v>-4.852209768000002</v>
       </c>
       <c r="P92">
-        <v>-17.78384168</v>
+        <v>-18.25355103200001</v>
       </c>
       <c r="Q92">
-        <v>10.51615832</v>
+        <v>10.04644896799999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5821468524962384</v>
+        <v>0.6417409472180426</v>
       </c>
       <c r="T92">
-        <v>9.043578460564737</v>
+        <v>10.0484205117386</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1216567928443829</v>
+        <v>0.1203199050109281</v>
       </c>
       <c r="W92">
-        <v>0.1763713159968479</v>
+        <v>0.1766397630738056</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5793180611637281</v>
+        <v>0.5729519286234672</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2184988696467869</v>
+        <v>0.220048869646787</v>
       </c>
       <c r="C93">
-        <v>-90.73135324877254</v>
+        <v>-94.60497258226007</v>
       </c>
       <c r="D93">
-        <v>157.6196467512275</v>
+        <v>156.70702741774</v>
       </c>
       <c r="E93">
-        <v>170.851</v>
+        <v>173.812</v>
       </c>
       <c r="F93">
-        <v>269.451</v>
+        <v>272.412</v>
       </c>
       <c r="G93">
         <v>21.1</v>
@@ -8913,37 +8913,37 @@
         <v>31</v>
       </c>
       <c r="M93">
-        <v>54.10576080000001</v>
+        <v>54.70032960000001</v>
       </c>
       <c r="N93">
-        <v>-23.10576080000001</v>
+        <v>-23.70032960000001</v>
       </c>
       <c r="O93">
-        <v>-4.852209768000002</v>
+        <v>-4.977069216000003</v>
       </c>
       <c r="P93">
-        <v>-18.25355103200001</v>
+        <v>-18.72326038400001</v>
       </c>
       <c r="Q93">
-        <v>10.04644896799999</v>
+        <v>9.57673961599999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6417409472180426</v>
+        <v>0.7162335656202984</v>
       </c>
       <c r="T93">
-        <v>10.0484205117386</v>
+        <v>11.30447307570593</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1203199050109281</v>
+        <v>0.1190120799564615</v>
       </c>
       <c r="W93">
-        <v>0.1766397630738056</v>
+        <v>0.1769023743447425</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5729519286234672</v>
+        <v>0.5667241902688643</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.220048869646787</v>
+        <v>0.221598869646787</v>
       </c>
       <c r="C94">
-        <v>-94.60497258226007</v>
+        <v>-98.46808460302913</v>
       </c>
       <c r="D94">
-        <v>156.70702741774</v>
+        <v>155.8049153969709</v>
       </c>
       <c r="E94">
-        <v>173.812</v>
+        <v>176.7730000000001</v>
       </c>
       <c r="F94">
-        <v>272.412</v>
+        <v>275.373</v>
       </c>
       <c r="G94">
         <v>21.1</v>
@@ -8995,37 +8995,37 @@
         <v>31</v>
       </c>
       <c r="M94">
-        <v>54.70032960000001</v>
+        <v>55.29489840000001</v>
       </c>
       <c r="N94">
-        <v>-23.70032960000001</v>
+        <v>-24.29489840000001</v>
       </c>
       <c r="O94">
-        <v>-4.977069216000003</v>
+        <v>-5.101928664000003</v>
       </c>
       <c r="P94">
-        <v>-18.72326038400001</v>
+        <v>-19.19296973600001</v>
       </c>
       <c r="Q94">
-        <v>9.57673961599999</v>
+        <v>9.107030263999992</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7162335656202984</v>
+        <v>0.8120097892803411</v>
       </c>
       <c r="T94">
-        <v>11.30447307570593</v>
+        <v>12.91939780080677</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1190120799564615</v>
+        <v>0.1177323801719834</v>
       </c>
       <c r="W94">
-        <v>0.1769023743447425</v>
+        <v>0.1771593380614657</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5667241902688643</v>
+        <v>0.5606303817713496</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.221598869646787</v>
+        <v>0.223148869646787</v>
       </c>
       <c r="C95">
-        <v>-98.46808460302913</v>
+        <v>-102.3208697341151</v>
       </c>
       <c r="D95">
-        <v>155.8049153969709</v>
+        <v>154.913130265885</v>
       </c>
       <c r="E95">
-        <v>176.7730000000001</v>
+        <v>179.7340000000001</v>
       </c>
       <c r="F95">
-        <v>275.373</v>
+        <v>278.3340000000001</v>
       </c>
       <c r="G95">
         <v>21.1</v>
@@ -9077,37 +9077,37 @@
         <v>31</v>
       </c>
       <c r="M95">
-        <v>55.29489840000001</v>
+        <v>55.88946720000001</v>
       </c>
       <c r="N95">
-        <v>-24.29489840000001</v>
+        <v>-24.88946720000002</v>
       </c>
       <c r="O95">
-        <v>-5.101928664000003</v>
+        <v>-5.226788112000003</v>
       </c>
       <c r="P95">
-        <v>-19.19296973600001</v>
+        <v>-19.66267908800001</v>
       </c>
       <c r="Q95">
-        <v>9.107030263999992</v>
+        <v>8.637320911999989</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8120097892803411</v>
+        <v>0.9397114208270647</v>
       </c>
       <c r="T95">
-        <v>12.91939780080677</v>
+        <v>15.07263076760791</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1177323801719834</v>
+        <v>0.1164799080424942</v>
       </c>
       <c r="W95">
-        <v>0.1771593380614657</v>
+        <v>0.1774108344650672</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5606303817713496</v>
+        <v>0.554666228773782</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.223148869646787</v>
+        <v>0.224698869646787</v>
       </c>
       <c r="C96">
-        <v>-102.3208697341151</v>
+        <v>-106.1635042912917</v>
       </c>
       <c r="D96">
-        <v>154.913130265885</v>
+        <v>154.0314957087083</v>
       </c>
       <c r="E96">
-        <v>179.7340000000001</v>
+        <v>182.695</v>
       </c>
       <c r="F96">
-        <v>278.3340000000001</v>
+        <v>281.295</v>
       </c>
       <c r="G96">
         <v>21.1</v>
@@ -9159,37 +9159,37 @@
         <v>31</v>
       </c>
       <c r="M96">
-        <v>55.88946720000001</v>
+        <v>56.484036</v>
       </c>
       <c r="N96">
-        <v>-24.88946720000002</v>
+        <v>-25.48403600000001</v>
       </c>
       <c r="O96">
-        <v>-5.226788112000003</v>
+        <v>-5.351647560000001</v>
       </c>
       <c r="P96">
-        <v>-19.66267908800001</v>
+        <v>-20.13238844000001</v>
       </c>
       <c r="Q96">
-        <v>8.637320911999989</v>
+        <v>8.167611559999994</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9397114208270647</v>
+        <v>1.118493704992478</v>
       </c>
       <c r="T96">
-        <v>15.07263076760791</v>
+        <v>18.08715692112949</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1164799080424942</v>
+        <v>0.1152538037473101</v>
       </c>
       <c r="W96">
-        <v>0.1774108344650672</v>
+        <v>0.1776570362075401</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.554666228773782</v>
+        <v>0.5488276368919529</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.224698869646787</v>
+        <v>0.226248869646787</v>
       </c>
       <c r="C97">
-        <v>-106.1635042912917</v>
+        <v>-109.9961605992853</v>
       </c>
       <c r="D97">
-        <v>154.0314957087083</v>
+        <v>153.1598394007147</v>
       </c>
       <c r="E97">
-        <v>182.695</v>
+        <v>185.656</v>
       </c>
       <c r="F97">
-        <v>281.295</v>
+        <v>284.256</v>
       </c>
       <c r="G97">
         <v>21.1</v>
@@ -9241,37 +9241,37 @@
         <v>31</v>
       </c>
       <c r="M97">
-        <v>56.484036</v>
+        <v>57.07860480000001</v>
       </c>
       <c r="N97">
-        <v>-25.48403600000001</v>
+        <v>-26.07860480000001</v>
       </c>
       <c r="O97">
-        <v>-5.351647560000001</v>
+        <v>-5.476507008000002</v>
       </c>
       <c r="P97">
-        <v>-20.13238844000001</v>
+        <v>-20.60209779200001</v>
       </c>
       <c r="Q97">
-        <v>8.167611559999994</v>
+        <v>7.697902207999991</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.118493704992478</v>
+        <v>1.386667131240598</v>
       </c>
       <c r="T97">
-        <v>18.08715692112949</v>
+        <v>22.60894615141188</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1152538037473101</v>
+        <v>0.1140532432916089</v>
       </c>
       <c r="W97">
-        <v>0.1776570362075401</v>
+        <v>0.1778981087470449</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5488276368919529</v>
+        <v>0.543110682340995</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2262488696467869</v>
+        <v>0.227798869646787</v>
       </c>
       <c r="C98">
-        <v>-109.9961605992853</v>
+        <v>-113.8190071040649</v>
       </c>
       <c r="D98">
-        <v>153.1598394007147</v>
+        <v>152.2979928959352</v>
       </c>
       <c r="E98">
-        <v>185.656</v>
+        <v>188.617</v>
       </c>
       <c r="F98">
-        <v>284.256</v>
+        <v>287.217</v>
       </c>
       <c r="G98">
         <v>21.1</v>
@@ -9323,37 +9323,37 @@
         <v>31</v>
       </c>
       <c r="M98">
-        <v>57.07860480000001</v>
+        <v>57.67317360000001</v>
       </c>
       <c r="N98">
-        <v>-26.07860480000001</v>
+        <v>-26.67317360000002</v>
       </c>
       <c r="O98">
-        <v>-5.476507008000002</v>
+        <v>-5.601366456000004</v>
       </c>
       <c r="P98">
-        <v>-20.60209779200001</v>
+        <v>-21.07180714400001</v>
       </c>
       <c r="Q98">
-        <v>7.697902207999991</v>
+        <v>7.228192855999989</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.386667131240595</v>
+        <v>1.833622841654127</v>
       </c>
       <c r="T98">
-        <v>22.60894615141182</v>
+        <v>30.14526153521576</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1140532432916089</v>
+        <v>0.1128774366597367</v>
       </c>
       <c r="W98">
-        <v>0.1778981087470449</v>
+        <v>0.1781342107187249</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.543110682340995</v>
+        <v>0.5375116031416032</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.227798869646787</v>
+        <v>0.229348869646787</v>
       </c>
       <c r="C99">
-        <v>-113.8190071040649</v>
+        <v>-117.632208481362</v>
       </c>
       <c r="D99">
-        <v>152.2979928959352</v>
+        <v>151.445791518638</v>
       </c>
       <c r="E99">
-        <v>188.617</v>
+        <v>191.578</v>
       </c>
       <c r="F99">
-        <v>287.217</v>
+        <v>290.178</v>
       </c>
       <c r="G99">
         <v>21.1</v>
@@ -9405,37 +9405,37 @@
         <v>31</v>
       </c>
       <c r="M99">
-        <v>57.67317360000001</v>
+        <v>58.2677424</v>
       </c>
       <c r="N99">
-        <v>-26.67317360000002</v>
+        <v>-27.26774240000001</v>
       </c>
       <c r="O99">
-        <v>-5.601366456000004</v>
+        <v>-5.726225904000001</v>
       </c>
       <c r="P99">
-        <v>-21.07180714400001</v>
+        <v>-21.54151649600001</v>
       </c>
       <c r="Q99">
-        <v>7.228192855999989</v>
+        <v>6.758483503999994</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.833622841654127</v>
+        <v>2.72753426248119</v>
       </c>
       <c r="T99">
-        <v>30.14526153521576</v>
+        <v>45.21789230282364</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1128774366597367</v>
+        <v>0.1117256260815761</v>
       </c>
       <c r="W99">
-        <v>0.1781342107187249</v>
+        <v>0.1783654942828195</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5375116031416032</v>
+        <v>0.5320267908646482</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.229348869646787</v>
+        <v>0.230898869646787</v>
       </c>
       <c r="C100">
-        <v>-117.632208481362</v>
+        <v>-121.4359257415686</v>
       </c>
       <c r="D100">
-        <v>151.445791518638</v>
+        <v>150.6030742584314</v>
       </c>
       <c r="E100">
-        <v>191.578</v>
+        <v>194.539</v>
       </c>
       <c r="F100">
-        <v>290.178</v>
+        <v>293.139</v>
       </c>
       <c r="G100">
         <v>21.1</v>
@@ -9487,37 +9487,37 @@
         <v>31</v>
       </c>
       <c r="M100">
-        <v>58.2677424</v>
+        <v>58.8623112</v>
       </c>
       <c r="N100">
-        <v>-27.26774240000001</v>
+        <v>-27.8623112</v>
       </c>
       <c r="O100">
-        <v>-5.726225904000001</v>
+        <v>-5.851085352000001</v>
       </c>
       <c r="P100">
-        <v>-21.54151649600001</v>
+        <v>-22.011225848</v>
       </c>
       <c r="Q100">
-        <v>6.758483503999994</v>
+        <v>6.288774151999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.72753426248119</v>
+        <v>5.409268524962379</v>
       </c>
       <c r="T100">
-        <v>45.21789230282364</v>
+        <v>90.43578460564729</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1117256260815761</v>
+        <v>0.1105970844039844</v>
       </c>
       <c r="W100">
-        <v>0.1783654942828195</v>
+        <v>0.1785921054516799</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5320267908646482</v>
+        <v>0.5266527828761165</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.230898869646787</v>
-      </c>
-      <c r="C101">
-        <v>-121.4359257415686</v>
-      </c>
-      <c r="D101">
-        <v>150.6030742584314</v>
-      </c>
-      <c r="E101">
-        <v>194.539</v>
-      </c>
-      <c r="F101">
-        <v>293.139</v>
-      </c>
-      <c r="G101">
-        <v>21.1</v>
-      </c>
-      <c r="H101">
-        <v>197.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>59.3</v>
-      </c>
-      <c r="K101">
-        <v>28.3</v>
-      </c>
-      <c r="L101">
-        <v>31</v>
-      </c>
-      <c r="M101">
-        <v>58.8623112</v>
-      </c>
-      <c r="N101">
-        <v>-27.8623112</v>
-      </c>
-      <c r="O101">
-        <v>-5.851085352000001</v>
-      </c>
-      <c r="P101">
-        <v>-22.011225848</v>
-      </c>
-      <c r="Q101">
-        <v>6.288774151999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.409268524962379</v>
-      </c>
-      <c r="T101">
-        <v>90.43578460564729</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1105970844039844</v>
-      </c>
-      <c r="W101">
-        <v>0.1785921054516799</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5266527828761165</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
